--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,14 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -459,30 +459,2046 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1510407</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>28.642,47</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>R$ 28.642,47</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1520612</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>53.357,33</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R$ 53.357,33</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1520615</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22.840,59</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>294.803,26</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-R$ 271.962,67</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-92.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1563492</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>145.164,32</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>294.803,26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-R$ 149.638,94</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-50.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1641139I</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1657713</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>83.267,14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R$ 83.267,14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1658452</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7.792,10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R$ 7.792,10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1663556</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.470,38</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R$ 2.470,38</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1671139I</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6.138,54</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R$ 6.138,54</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1676605</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>78.399,90</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R$ 78.399,90</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1677314</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>46.760,40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>R$ 46.760,40</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>1677316</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>51.623,62</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>R$ 51.623,62</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1688115C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6,36</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>R$ 6,36</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1688115I</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18.752,84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>R$ 18.752,84</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1694258</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>127.751,38</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>R$ 127.751,38</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1695716</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>74.647,17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R$ 74.647,17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1699516</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.388,62</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-R$ 26.762,16</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-88.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1702776C</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1702776I</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18.098,87</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>R$ 18.098,87</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1703223</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18.169,34</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>R$ 18.169,34</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1704476</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>111,28</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>R$ 111,28</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1704525</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15.365,48</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>R$ 15.365,48</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1704891</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>100.528,77</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>163.376,34</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-R$ 62.847,57</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-38.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1704968</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.808,15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>R$ 2.808,15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1708066</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3.419,06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>R$ 3.419,06</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1708877</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3,54</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>R$ 3,54</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1708877I</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.132,72</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>R$ 2.132,72</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1710735</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>9.153,35</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>R$ 9.153,35</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1710937</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.234,81</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>R$ 4.234,81</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1711384</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2.127,38</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>R$ 2.127,38</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1711525</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.998,42</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>R$ 1.998,42</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1712530</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5.393,72</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>R$ 5.393,72</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1712538</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3.955,41</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>R$ 3.955,41</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1712547</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7.069,45</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>R$ 7.069,45</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1712624</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3.073,90</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>R$ 3.073,90</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1712957</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2.222,83</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>R$ 2.222,83</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1713044C</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21,11</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>R$ 21,11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1713044I</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1.528,53</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>R$ 1.528,53</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1713221</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>18.794,09</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>R$ 18.794,09</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1713226</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3.049,11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>R$ 3.049,11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1713240</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5.108,11</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>R$ 5.108,11</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1713262</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2.675,61</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>R$ 2.675,61</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1713679</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>3.574,44</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>R$ 3.574,44</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1713719</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3.385,92</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>R$ 3.385,92</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1713933</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5.530,92</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>R$ 5.530,92</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1714909</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.062,57</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>R$ 1.062,57</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1715127</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4.418,94</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>R$ 4.418,94</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1715327</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5.483,37</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>R$ 5.483,37</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1715668</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.070,47</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>R$ 2.070,47</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1715688</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>9.669,94</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>73.801,59</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-R$ 64.131,65</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-86.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.786,71</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>R$ 1.786,71</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1715920</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1.031,94</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>R$ 1.031,94</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2.496,51</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>R$ 2.496,51</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1718435</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>17.153,90</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>40.717,37</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>-R$ 23.563,47</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-57.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3.206,15</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>R$ 3.206,15</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1718555I</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2.781,60</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>R$ 2.781,60</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3.077,85</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>R$ 3.077,85</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1719097</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7.450,28</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>-R$ 10.084,35</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-57.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>960,92</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>R$ 960,92</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1719155</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2.223,15</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>-R$ 27.927,63</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-92.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3.239,73</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>R$ 3.239,73</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1719881H</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>38.258,42</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>R$ 38.258,42</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1720116</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.675,57</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>28.774,45</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>-R$ 27.098,88</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-94.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>555,60</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>R$ 555,60</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18.169,34</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 18.169,34</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1355,12 +1355,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 2.127,38</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 2.127,38</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 3.049,11</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 3.049,11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 4.418,94</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 2.070,47</t>
+          <t>R$ 4.418,94</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2027,44 +2027,44 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.070,47</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,44 +2091,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,44 +2155,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,44 +2219,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,44 +2283,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,22 +2347,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2372,19 +2372,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2411,94 +2411,158 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 27.927,63</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.6%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.675,57</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-R$ 27.098,88</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-94.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>1719881H</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>38.258,42</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>R$ 38.258,42</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1720116</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1.844,52</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>28.774,45</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-R$ 26.929,93</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-93.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>1720920</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>555,60</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>R$ 555,60</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -619,12 +619,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -651,12 +651,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -683,12 +683,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 6,36</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 18.752,84</t>
+          <t>R$ 46.760,40</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 51.623,62</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 6,36</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,44 +971,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>18.752,84</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 18.752,84</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,44 +1099,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 111,28</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1163,44 +1163,44 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-R$ 62.847,57</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 111,28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,44 +1323,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 62.847,57</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.5%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 2.127,38</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>2.127,38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 2.127,38</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 3.049,11</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>3.049,11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 3.049,11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 4.418,94</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 2.070,47</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,44 +2091,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>4.418,94</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 4.418,94</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,76 +2219,76 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.070,47</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.070,47</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,108 +2347,108 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,62 +2507,286 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>1719097</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7.450,28</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>-R$ 10.084,35</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-57.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>960,92</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>R$ 960,92</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1719155</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2.223,15</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>-R$ 27.927,63</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-92.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>3.239,73</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>R$ 3.239,73</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1719881H</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>38.258,42</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>R$ 38.258,42</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1720116</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1.844,52</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>28.774,45</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>-R$ 26.929,93</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-93.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>1720920</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>555,60</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>R$ 555,60</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 6,36</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18.752,84</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 18.752,84</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.127,38</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 2.127,38</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 46.760,40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 51.623,62</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,44 +1099,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,44 +1195,44 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 111,28</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,44 +1323,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-R$ 62.847,57</t>
+          <t>R$ 111,28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,44 +1419,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>-R$ 62.847,57</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.5%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3.049,11</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 3.049,11</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4.418,94</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 4.418,94</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,12 +2219,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.070,47</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 2.070,47</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2251,44 +2251,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,44 +2379,44 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.654,77</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,44 +2475,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,44 +2539,44 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,22 +2603,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2628,19 +2628,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2699,44 +2699,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,32 +2763,320 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>1719097</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7.450,28</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>-R$ 10.084,35</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-57.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>960,92</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>R$ 960,92</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1719155</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2.223,15</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>-R$ 27.927,63</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-92.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>3.239,73</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>R$ 3.239,73</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1719881H</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>38.258,42</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>R$ 38.258,42</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1720116</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.844,52</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>28.774,45</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>-R$ 26.929,93</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-93.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>555,60</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>R$ 555,60</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>1724341</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>40.758,00</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>R$ 40.758,00</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -587,39 +587,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1564187</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107.041,70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>128.182,85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.141,15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,12 +651,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R$ 59.714,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -683,12 +683,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 46.760,40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 51.623,62</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 20.334,45</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,76 +1195,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 20.525,53</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,22 +1291,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 1.866,87</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1316,51 +1316,51 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 111,28</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,44 +1419,44 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-R$ 62.847,57</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 111,28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,44 +1547,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>100.528,77</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 62.847,57</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-38.5%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1611,44 +1611,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 4.402,38</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,44 +1931,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>-R$ 427,34</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 4.585,98</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,12 +2219,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2251,12 +2251,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 2.654,77</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2411,44 +2411,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,44 +2475,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,108 +2603,108 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 20.238,41</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,44 +2763,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,44 +2827,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 6.987,28</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 2.654,77</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,44 +2923,44 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2987,96 +2987,1280 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>1715816I</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>3.168,40</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>R$ 3.168,40</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1715878</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1.786,71</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>R$ 1.786,71</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1715899</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>3.389,65</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>-R$ 26.761,13</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-88.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1715920</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1.031,94</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>R$ 1.031,94</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1715955I</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2.970,68</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>R$ 2.970,68</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1717166</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>22.116,83</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>73.801,59</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>-R$ 51.684,76</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-70.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1717168</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2.528,74</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>-R$ 27.622,04</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-91.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1717332</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2.496,51</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>R$ 2.496,51</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1718435</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>17.153,90</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>40.717,37</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>-R$ 23.563,47</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-57.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1718442</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>3.206,15</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>R$ 3.206,15</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1718555I</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2.781,60</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>R$ 2.781,60</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1718561</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>13.683,99</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>R$ 13.683,99</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1718803</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>3.825,18</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>R$ 3.825,18</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1719070</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3.077,85</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>R$ 3.077,85</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1719097</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>7.450,28</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>-R$ 10.084,35</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-57.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1719135</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>960,92</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>R$ 960,92</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1719155</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2.223,15</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>-R$ 27.927,63</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-92.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1719213</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5.951,32</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>30.150,78</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>-R$ 24.199,46</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-80.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1719214</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>6.124,60</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>28.774,45</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>-R$ 22.649,85</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-78.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1719881</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>3.239,73</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>R$ 3.239,73</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1719881H</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>38.258,42</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>R$ 38.258,42</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1720116</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.844,52</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>28.774,45</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>-R$ 26.929,93</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-93.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1720721</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2.015,45</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>-R$ 15.519,18</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-88.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1720914</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>13.736,92</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>55.022,87</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>-R$ 41.285,95</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>555,60</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>R$ 555,60</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1721631</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>12.649,43</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>R$ 12.649,43</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1721631C</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>100,65</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>-R$ 17.433,98</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>807,18</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>-R$ 24.194,92</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-96.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1721886</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>14.551,70</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>55.022,87</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>-R$ 40.471,17</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-73.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1721887</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>15.229,27</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>-R$ 45.688,83</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1722169</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>38.238,91</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>R$ 38.238,91</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7.614,80</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>-R$ 53.303,30</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>14.377,51</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>R$ 14.377,51</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>1725738I</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>15.544,67</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>25.002,10</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>-R$ 9.457,43</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>❌ PREJUÍZO</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1728163</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7.914,69</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>R$ 7.914,69</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 38.435,91</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 46.760,40</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 51.623,62</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 20.334,45</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 20.334,45</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,86 +1227,86 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-R$ 20.525,53</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>-R$ 20.525,53</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 1.866,87</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1316,83 +1316,83 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 1.866,87</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 111,28</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 111,28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,86 +1547,86 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>100.528,77</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-R$ 62.847,57</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>-R$ 6.281,32</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1636,51 +1636,51 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,76 +1707,76 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 4.402,38</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 4.402,38</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1931,44 +1931,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-R$ 427,34</t>
+          <t>R$ 24.209,42</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,22 +2059,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2084,19 +2084,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 4.585,98</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,44 +2123,44 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>-R$ 427,34</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2219,12 +2219,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2251,12 +2251,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 4.585,98</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2411,44 +2411,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,108 +2603,108 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-R$ 20.238,41</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,12 +2763,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,76 +2827,76 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 6.987,28</t>
+          <t>-R$ 20.238,41</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 2.654,77</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2987,44 +2987,44 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 6.987,28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.654,77</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,44 +3115,44 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3179,108 +3179,108 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-R$ 27.622,04</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,19 +3332,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,76 +3403,76 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 13.683,99</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 27.622,04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.6%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,22 +3499,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,108 +3563,108 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-R$ 24.199,46</t>
+          <t>R$ 13.683,99</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,22 +3723,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3748,61 +3748,61 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>-R$ 27.927,63</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3812,157 +3812,157 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-92.6%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>-R$ 24.199,46</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-80.3%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-R$ 24.194,92</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3972,29 +3972,29 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4004,51 +4004,51 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 38.238,91</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>R$ 555,60</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4075,86 +4075,86 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 14.377,51</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>-R$ 24.194,92</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4164,29 +4164,29 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4196,29 +4196,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4228,37 +4228,293 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>1722169</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>38.238,91</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>R$ 38.238,91</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1722779</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>14.090,54</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>205.265,15</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-R$ 191.174,61</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-93.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7.614,80</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-R$ 53.303,30</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>14.377,51</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>R$ 14.377,51</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
           <t>1728163</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>7.914,69</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>R$ 7.914,69</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -491,12 +491,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1520612</t>
+          <t>1513223</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>110.020,78</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R$ 53.357,33</t>
+          <t>R$ 110.020,78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -523,44 +523,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1520615</t>
+          <t>1520612</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.840,59</t>
+          <t>53.357,33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-R$ 271.962,67</t>
+          <t>R$ 53.357,33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-92.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1520615</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145.164,32</t>
+          <t>22.840,59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-R$ 149.638,94</t>
+          <t>-R$ 271.962,67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -580,29 +580,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-92.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1564187</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>107.041,70</t>
+          <t>145.164,32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>128.182,85</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-R$ 21.141,15</t>
+          <t>-R$ 149.638,94</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -612,46 +612,46 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-50.8%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1564187</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107.041,70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>128.182,85</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.141,15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -683,12 +683,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R$ 59.714,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38.435,91</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 38.435,91</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>38.435,91</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 38.435,91</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 46.760,40</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 51.623,62</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 20.334,45</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,44 +1259,44 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-R$ 20.525,53</t>
+          <t>R$ 20.334,45</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,22 +1323,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 1.866,87</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1348,29 +1348,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>-R$ 20.525,53</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1380,19 +1380,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1419,22 +1419,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 1.866,87</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1444,51 +1444,51 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 111,28</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1579,150 +1579,150 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>111,28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-R$ 6.281,32</t>
+          <t>R$ 111,28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>-R$ 6.281,32</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1732,29 +1732,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1764,19 +1764,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,76 +1803,76 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 4.402,38</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 24.209,42</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 4.402,38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 24.209,42</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,22 +2059,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2084,19 +2084,19 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,54 +2123,54 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-R$ 427,34</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2219,44 +2219,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>-R$ 427,34</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 4.585,98</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>4.585,98</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 4.585,98</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,44 +2603,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2699,44 +2699,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,12 +2763,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,76 +2827,76 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 20.238,41</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,76 +2923,76 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>-R$ 20.238,41</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 6.987,28</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 2.654,77</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 6.987,28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3179,44 +3179,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 2.654,77</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,76 +3275,76 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,22 +3403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3428,51 +3428,51 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-R$ 27.622,04</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,22 +3499,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3524,51 +3524,51 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>2.528,74</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 27.622,04</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.6%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,44 +3595,44 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 13.683,99</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,12 +3659,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 13.683,99</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,44 +3723,44 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,54 +3787,54 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-R$ 24.199,46</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3844,115 +3844,115 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 27.927,63</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.6%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 24.199,46</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-80.3%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3972,157 +3972,157 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4132,93 +4132,93 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-R$ 24.194,92</t>
+          <t>R$ 555,60</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4228,61 +4228,61 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>807,18</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 38.238,91</t>
+          <t>-R$ 24.194,92</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4292,157 +4292,157 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>38.238,91</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>R$ 38.238,91</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 14.377,51</t>
+          <t>-R$ 191.174,61</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4452,69 +4452,165 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>14.377,51</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>R$ 14.377,51</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>1728163</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>7.914,69</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
         <is>
           <t>R$ 7.914,69</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>9.678,68</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 9.678,68</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 100,65</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 11.953,89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>46.760,40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 46.760,40</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 51.623,62</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 20.334,45</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1355,44 +1355,44 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-R$ 20.525,53</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,22 +1419,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>20.334,45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 1.866,87</t>
+          <t>R$ 20.334,45</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1444,51 +1444,51 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,44 +1547,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>-R$ 20.525,53</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>111,28</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 111,28</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,22 +1643,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 1.866,87</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1668,61 +1668,61 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-R$ 6.281,32</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1732,51 +1732,51 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1803,76 +1803,76 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,108 +1963,108 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 4.402,38</t>
+          <t>-R$ 6.281,32</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 24.209,42</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,76 +2123,76 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,44 +2219,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-R$ 427,34</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 4.402,38</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4.585,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 4.585,98</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 24.209,42</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,22 +2603,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2628,19 +2628,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,76 +2667,76 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>-R$ 427,34</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,12 +2763,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,76 +2923,76 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>-R$ 20.238,41</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 6.987,28</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3179,44 +3179,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 2.654,77</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,44 +3275,44 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3339,12 +3339,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,22 +3403,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>-R$ 20.238,41</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3428,19 +3428,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,108 +3467,108 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2.528,74</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-R$ 27.622,04</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,44 +3595,44 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 6.987,28</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,12 +3659,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 13.683,99</t>
+          <t>R$ 2.654,77</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,76 +3787,76 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,44 +3883,44 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-R$ 24.199,46</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3940,51 +3940,51 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,54 +4011,54 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4068,61 +4068,61 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,246 +4203,246 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>R$ 13.683,99</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>807,18</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>-R$ 24.194,92</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>38.238,91</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 38.238,91</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 27.927,63</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.6%</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 24.199,46</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4452,125 +4452,125 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-80.3%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 14.377,51</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4580,37 +4580,549 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>1720721</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2.015,45</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>-R$ 15.519,18</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-88.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1720914</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>13.736,92</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>55.022,87</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>-R$ 41.285,95</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1720920</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>555,60</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>R$ 555,60</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1721631</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>12.649,43</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>R$ 12.649,43</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1721631C</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>100,65</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>-R$ 17.433,98</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>940,27</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>-R$ 24.061,83</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-96.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1721886</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>14.551,70</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>55.022,87</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>-R$ 40.471,17</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-73.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1721887</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>15.229,27</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>-R$ 45.688,83</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1722169</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>39.464,29</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>R$ 39.464,29</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1722779</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>14.090,54</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>205.265,15</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>-R$ 191.174,61</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-93.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>7.614,80</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>-R$ 53.303,30</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>14.377,51</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>R$ 14.377,51</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
           <t>1728163</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>7.914,69</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
         <is>
           <t>R$ 7.914,69</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,76 +1547,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-R$ 20.525,53</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>-R$ 20.525,53</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,22 +1643,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 1.866,87</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1668,29 +1668,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 1.866,87</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1700,83 +1700,83 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,86 +1963,86 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>15.365,48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-R$ 6.281,32</t>
+          <t>R$ 15.365,48</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 6.281,32</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2052,179 +2052,179 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2251,44 +2251,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 4.402,38</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 24.209,42</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>4.402,38</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 4.402,38</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24.209,42</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,44 +2603,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,44 +2667,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-R$ 427,34</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,22 +2763,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2788,19 +2788,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>1.998,42</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 1.998,42</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,44 +2827,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>1.928,86</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>-R$ 427,34</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.1%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3179,44 +3179,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3339,44 +3339,44 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,44 +3403,44 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-R$ 20.238,41</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,44 +3467,44 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,44 +3595,44 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>-R$ 20.238,41</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 6.987,28</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,44 +3659,44 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 2.654,77</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,44 +3787,44 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>6.987,28</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 6.987,28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,44 +3915,44 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>2.654,77</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 2.654,77</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3979,12 +3979,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>9.669,94</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>-R$ 64.131,65</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4036,51 +4036,51 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-86.9%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4107,76 +4107,76 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,12 +4203,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 13.683,99</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,76 +4235,76 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,22 +4331,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4356,19 +4356,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,108 +4395,108 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>13.683,99</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-R$ 24.199,46</t>
+          <t>R$ 13.683,99</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4523,12 +4523,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4555,22 +4555,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4580,61 +4580,61 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>2.223,15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>-R$ 27.927,63</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4644,157 +4644,157 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-92.6%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>5.951,32</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>-R$ 24.199,46</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-80.3%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4804,29 +4804,29 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4836,83 +4836,83 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>555,60</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>R$ 555,60</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4939,22 +4939,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4964,61 +4964,61 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 14.377,51</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5028,29 +5028,29 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5060,69 +5060,293 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>1722779</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>14.090,54</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>205.265,15</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>-R$ 191.174,61</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-93.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7.614,80</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-R$ 53.303,30</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>14.377,51</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>24.535,37</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-R$ 10.157,86</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-41.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>1728163</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>7.914,69</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
         <is>
           <t>R$ 7.914,69</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 1.065,14</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.273,55</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>46.760,40</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 46.760,40</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 51.623,62</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,22 +1259,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1284,29 +1284,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1316,19 +1316,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1355,12 +1355,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20.334,45</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 20.334,45</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1579,44 +1579,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-R$ 20.525,53</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,22 +1675,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 1.866,87</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1700,83 +1700,83 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>4.476,57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>-R$ 20.525,53</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,44 +1803,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.966,25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.866,87</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+26.3%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1867,44 +1867,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>3.388,62</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>-R$ 26.762,16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15.365,48</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 15.365,48</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,108 +2027,108 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>-R$ 6.281,32</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,22 +2187,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>158.642,45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>-R$ 6.281,32</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2212,61 +2212,61 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-3.8%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2276,19 +2276,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,44 +2347,44 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,44 +2411,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4.402,38</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 4.402,38</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 24.209,42</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2603,44 +2603,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2699,12 +2699,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>24.209,42</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24.209,42</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,44 +2763,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.998,42</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 1.998,42</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,44 +2827,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.928,86</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 427,34</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,22 +2923,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2948,19 +2948,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2987,44 +2987,44 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3339,44 +3339,44 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,12 +3403,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3435,12 +3435,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,44 +3499,44 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3595,44 +3595,44 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>-R$ 20.238,41</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,44 +3659,44 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,44 +3851,44 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6.987,28</t>
+          <t>1.949,56</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 6.987,28</t>
+          <t>-R$ 20.238,41</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.2%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,44 +3915,44 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2.654,77</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 2.654,77</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3979,12 +3979,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,44 +4011,44 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>9.669,94</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 64.131,65</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-86.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4107,12 +4107,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4139,44 +4139,44 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,12 +4203,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,140 +4235,140 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,44 +4427,44 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>13.683,99</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 13.683,99</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4491,12 +4491,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4523,54 +4523,54 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4580,93 +4580,93 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2.223,15</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>-R$ 27.927,63</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>-92.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5.951,32</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-R$ 24.199,46</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4676,51 +4676,51 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4779,54 +4779,54 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4836,51 +4836,51 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>555,60</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 555,60</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4907,86 +4907,86 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4996,29 +4996,29 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5028,29 +5028,29 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5060,19 +5060,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5099,86 +5099,86 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5188,29 +5188,29 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-R$ 10.157,86</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5220,29 +5220,29 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5252,101 +5252,741 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>1721631C</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>100,65</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>17.534,63</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>-R$ 17.433,98</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1721869</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>940,27</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-R$ 24.061,83</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-96.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1721886</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>14.551,70</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>55.022,87</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-R$ 40.471,17</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-73.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1721887</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>15.229,27</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-R$ 45.688,83</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1722165</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>23.880,34</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>294.803,26</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-R$ 270.922,92</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-91.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1722169</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>39.464,29</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>R$ 39.464,29</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1722779</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>14.090,54</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>205.265,15</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-R$ 191.174,61</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-93.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1722904</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2.417,20</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-R$ 22.584,90</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-90.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>7.614,80</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-R$ 53.303,30</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>14.377,51</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>24.535,37</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-R$ 10.157,86</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-41.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1725869</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>R$ 2.488,83</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>52.831,30</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>192.548,30</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>-R$ 139.717,00</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-72.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1726044</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>68.094,35</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>167.292,84</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-R$ 99.198,49</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-59.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1726045</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>59.559,30</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>126.996,75</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>-R$ 67.437,45</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-53.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1726057</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>98.316,97</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>196.508,79</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>-R$ 98.191,82</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1726058</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>28.638,24</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>133.354,34</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>-R$ 104.716,10</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-78.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>1728163</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>7.914,69</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
         <is>
           <t>R$ 7.914,69</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -587,54 +587,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1563492</t>
+          <t>1536912</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>145.164,32</t>
+          <t>2.474,56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-R$ 149.638,94</t>
+          <t>R$ 2.474,56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1564187</t>
+          <t>1563492</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>107.041,70</t>
+          <t>145.164,32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>128.182,85</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-R$ 21.141,15</t>
+          <t>-R$ 149.638,94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -644,46 +644,46 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-50.8%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1564187</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107.041,70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>128.182,85</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.141,15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R$ 59.714,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38.435,91</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 38.435,91</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1659019</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9.678,68</t>
+          <t>40.789,42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 9.678,68</t>
+          <t>R$ 40.789,42</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>9.678,68</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 100,65</t>
+          <t>R$ 9.678,68</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 11.953,89</t>
+          <t>R$ 100,65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1663544</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.065,14</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 1.065,14</t>
+          <t>R$ 11.953,89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 1.065,14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1667134</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.273,55</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 1.273,55</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 1.273,55</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,22 +1259,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>51.640,54</t>
+          <t>78.399,90</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 51.500,65</t>
+          <t>R$ 78.399,90</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1284,19 +1284,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+36815.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 51.483,73</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+36803.0%</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 8,36</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1348,19 +1348,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,76 +1707,76 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4.476,57</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-R$ 20.525,53</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,22 +1803,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8.966,25</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 1.866,87</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1828,29 +1828,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+26.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1860,83 +1860,83 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.388,62</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-R$ 26.762,16</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,54 +2187,54 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>158.642,45</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-R$ 6.281,32</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2244,29 +2244,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2276,51 +2276,51 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,44 +2347,44 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2436,19 +2436,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,44 +2507,44 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2603,44 +2603,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2699,44 +2699,44 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>24.209,42</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 24.209,42</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,7 +2859,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,22 +2923,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2948,19 +2948,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2987,54 +2987,54 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3044,19 +3044,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,76 +3083,76 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3339,12 +3339,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,12 +3403,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3435,12 +3435,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,44 +3499,44 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,44 +3659,44 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,44 +3851,44 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.949,56</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-R$ 20.238,41</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,44 +3915,44 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3979,12 +3979,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4043,44 +4043,44 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4107,44 +4107,44 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,12 +4203,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,12 +4235,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,44 +4299,44 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,44 +4427,44 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4491,140 +4491,140 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,22 +4651,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4676,19 +4676,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,86 +4747,86 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4836,19 +4836,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4875,54 +4875,54 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4932,19 +4932,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4971,140 +4971,140 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,44 +5131,44 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5188,61 +5188,61 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5252,93 +5252,93 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5348,93 +5348,93 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5444,29 +5444,29 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5476,61 +5476,61 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5540,93 +5540,93 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5636,61 +5636,61 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>14.377,51</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-R$ 10.157,86</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5700,19 +5700,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5732,29 +5732,29 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5764,61 +5764,61 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5828,29 +5828,29 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>68.094,35</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 99.198,49</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5860,61 +5860,61 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>59.559,30</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-R$ 67.437,45</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>98.316,97</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 98.191,82</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5924,29 +5924,29 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>28.638,24</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 104.716,10</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5956,39 +5956,839 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
+          <t>1722779</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>14.090,54</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>205.265,15</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>-R$ 191.174,61</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-93.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1722904</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2.417,20</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-R$ 22.584,90</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-90.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1724051I</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.432,48</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>151.495,34</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-R$ 149.062,86</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-98.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1724172</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>23.068,97</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>-R$ 37.849,13</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-62.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1724341</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>40.758,00</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>R$ 40.758,00</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1724356</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>7.614,80</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>60.918,10</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-R$ 53.303,30</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-87.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1724491</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>14.410,93</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>24.535,37</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>-R$ 10.124,44</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-41.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1724551</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>7.181,35</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-R$ 52.022,30</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-87.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1725260</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>4.716,47</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>30.884,03</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-R$ 26.167,56</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-84.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1725686</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>11.172,87</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>24.535,37</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-R$ 13.362,50</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-54.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1725738C</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>140,91</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-R$ 24.861,19</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-99.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1725738I</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>15.544,67</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>25.002,10</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-R$ 9.457,43</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-37.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1725869</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>R$ 2.488,83</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>52.831,30</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>192.548,30</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>-R$ 139.717,00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-72.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1726044</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>68.094,35</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>167.292,84</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>-R$ 99.198,49</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-59.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1726045</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>59.559,30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>126.996,75</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>-R$ 67.437,45</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-53.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1726057</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>98.316,97</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>196.508,79</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>-R$ 98.191,82</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1726058</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>28.638,24</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>133.354,34</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>-R$ 104.716,10</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-78.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1726332</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>5.722,23</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>-R$ 23.174,51</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-80.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3.252,02</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>11.143,51</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>-R$ 7.891,49</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-70.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1727335</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>5.053,73</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>8.079,08</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>-R$ 3.025,35</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-37.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1727808I</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2.562,33</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>8.676,98</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>-R$ 6.114,65</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1728055</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>12.947,91</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>-R$ 29.152,92</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-69.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
           <t>1728163</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B198" t="inlineStr">
         <is>
           <t>7.914,69</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
         <is>
           <t>R$ 7.914,69</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>4.243,92</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-R$ 54.959,73</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-92.8%</t>
         </is>
       </c>
     </row>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.642,47</t>
+          <t>55.651,16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R$ 28.642,47</t>
+          <t>R$ 55.651,16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -651,71 +651,71 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1564187</t>
+          <t>1564134</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>107.041,70</t>
+          <t>44.646,20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>128.182,85</t>
+          <t>43.461,59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-R$ 21.141,15</t>
+          <t>R$ 1.184,61</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>+2.7%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1564187</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>107.041,70</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>128.182,85</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.141,15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-16.5%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R$ 59.714,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>40.789,42</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 40.789,42</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1659019</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9.678,68</t>
+          <t>40.789,42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 9.678,68</t>
+          <t>R$ 40.789,42</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>9.678,68</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 100,65</t>
+          <t>R$ 9.678,68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 11.953,89</t>
+          <t>R$ 100,65</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1663544</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.065,14</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 1.065,14</t>
+          <t>R$ 11.953,89</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 1.065,14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1667134</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.273,55</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 1.273,55</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 1.273,55</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>78.399,90</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 78.399,90</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,22 +1291,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>51.640,54</t>
+          <t>120.604,17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 51.500,65</t>
+          <t>R$ 120.604,17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1316,19 +1316,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+36815.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 51.483,73</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1348,29 +1348,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+36803.0%</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 8,36</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1380,19 +1380,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,76 +1739,76 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1860,29 +1860,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1892,83 +1892,83 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,54 +2219,54 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2276,29 +2276,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2308,51 +2308,51 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2411,76 +2411,76 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2507,76 +2507,76 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2699,76 +2699,76 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3019,22 +3019,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3044,29 +3044,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3076,61 +3076,61 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3140,51 +3140,51 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>5.393,72</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>R$ 5.393,72</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,12 +3307,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3339,12 +3339,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3403,12 +3403,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3435,12 +3435,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,76 +3659,76 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3979,12 +3979,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4043,108 +4043,108 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>7.890,42</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 1.016,35</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>+14.8%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,44 +4171,44 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,12 +4235,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4491,44 +4491,44 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4555,44 +4555,44 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4619,12 +4619,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,44 +4651,44 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4715,118 +4715,118 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4836,61 +4836,61 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4900,115 +4900,115 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,44 +5067,44 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,76 +5131,76 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,22 +5227,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>-R$ 45.453,71</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5252,29 +5252,29 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5284,61 +5284,61 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5348,83 +5348,83 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5444,93 +5444,93 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5540,61 +5540,61 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5604,29 +5604,29 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5636,19 +5636,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5675,22 +5675,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5700,29 +5700,29 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5732,61 +5732,61 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5796,29 +5796,29 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5828,29 +5828,29 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5860,61 +5860,61 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5924,29 +5924,29 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5956,61 +5956,61 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6020,29 +6020,29 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6052,29 +6052,29 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 191.174,61</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6084,61 +6084,61 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6148,29 +6148,29 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6180,61 +6180,61 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>7.181,35</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-R$ 52.022,30</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-87.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6244,19 +6244,19 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6276,29 +6276,29 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 13.137,83</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6308,29 +6308,29 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>7.181,35</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 52.022,30</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6340,61 +6340,61 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-87.9%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>4.716,47</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 26.167,56</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6404,29 +6404,29 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>68.094,35</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-R$ 99.198,49</t>
+          <t>-R$ 24.861,19</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6436,29 +6436,29 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>59.559,30</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-R$ 67.437,45</t>
+          <t>-R$ 9.457,43</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6468,61 +6468,61 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>98.316,97</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 98.191,82</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>28.638,24</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-R$ 104.716,10</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6532,29 +6532,29 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>68.094,35</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 99.198,49</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,29 +6564,29 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-59.3%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>59.559,30</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 67.437,45</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,29 +6596,29 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-53.1%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>98.316,97</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 98.191,82</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6628,61 +6628,61 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.638,24</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 104.716,10</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.5%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>2.048,89</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 17.166,37</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6692,29 +6692,29 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-89.3%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6724,69 +6724,261 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>1727335</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5.053,73</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>8.079,08</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>-R$ 3.025,35</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-37.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1727808I</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2.562,33</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>8.676,98</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>-R$ 6.114,65</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1728055</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>12.947,91</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>-R$ 29.152,92</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-69.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1728163</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>7.914,69</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>R$ 7.914,69</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>18.608,52</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>-R$ 10.288,22</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-35.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
           <t>1730763</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>4.243,92</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>59.203,65</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>-R$ 54.959,73</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>❌ PREJUÍZO</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>-92.8%</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,12 +715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1595636</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>760,40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 760,40</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R$ 59.714,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40.789,42</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 40.789,42</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1659019</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9.678,68</t>
+          <t>40.789,42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 9.678,68</t>
+          <t>R$ 40.789,42</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>9.678,68</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 100,65</t>
+          <t>R$ 9.678,68</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 11.953,89</t>
+          <t>R$ 100,65</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1663544</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.065,14</t>
+          <t>11.953,89</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 1.065,14</t>
+          <t>R$ 11.953,89</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 1.065,14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1667134</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.273,55</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 1.273,55</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 1.273,55</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>120.604,17</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 120.604,17</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,22 +1323,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>51.640,54</t>
+          <t>120.604,17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 51.500,65</t>
+          <t>R$ 120.604,17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1348,19 +1348,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+36815.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 51.483,73</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1380,29 +1380,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+36803.0%</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 8,36</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1412,19 +1412,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1451,12 +1451,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1579,12 +1579,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1771,76 +1771,76 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>74.647,17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 74.647,17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,22 +1867,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1892,29 +1892,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,83 +1924,83 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,44 +2187,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>36.411,37</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>-R$ 34.074,32</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2251,54 +2251,54 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2308,179 +2308,179 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,76 +2539,76 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2699,54 +2699,54 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2756,19 +2756,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2795,12 +2795,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2891,44 +2891,44 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.198,90</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2955,44 +2955,44 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3051,22 +3051,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3076,19 +3076,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,76 +3115,76 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5.393,72</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 5.393,72</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3243,44 +3243,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,19 +3332,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,76 +3371,76 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,12 +3467,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,12 +3659,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,44 +3691,44 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,44 +3947,44 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,12 +4011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4043,12 +4043,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4075,54 +4075,54 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7.890,42</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 1.016,35</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>+14.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,44 +4171,44 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,12 +4235,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,44 +4267,44 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>1.129,23</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>-R$ 12.353,05</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.6%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,54 +4427,54 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>7.890,42</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 1.016,35</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4484,19 +4484,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+14.8%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4523,76 +4523,76 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4619,12 +4619,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4715,44 +4715,44 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4811,204 +4811,204 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,44 +5067,44 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,118 +5131,118 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 45.453,71</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5252,93 +5252,93 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5348,115 +5348,115 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,86 +5483,86 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5572,29 +5572,29 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>24.975,36</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 20.877,68</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5604,93 +5604,93 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-45.5%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 45.453,71</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5700,93 +5700,93 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5796,29 +5796,29 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5828,29 +5828,29 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5860,93 +5860,93 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -5956,61 +5956,61 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6020,29 +6020,29 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6052,61 +6052,61 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6116,29 +6116,29 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6148,93 +6148,93 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6244,29 +6244,29 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6276,29 +6276,29 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 13.137,83</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6308,29 +6308,29 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7.181,35</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 52.022,30</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6340,29 +6340,29 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-87.9%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>4.716,47</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-R$ 26.167,56</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6372,61 +6372,61 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6436,29 +6436,29 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6468,61 +6468,61 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 191.174,61</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6532,29 +6532,29 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>68.094,35</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 99.198,49</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,29 +6564,29 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>59.559,30</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 67.437,45</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,29 +6596,29 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>98.316,97</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 98.191,82</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6628,61 +6628,61 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>28.638,24</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 104.716,10</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2.048,89</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 17.166,37</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6692,29 +6692,29 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-89.3%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6724,29 +6724,29 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 13.137,83</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6756,29 +6756,29 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6788,61 +6788,61 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.181,35</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 52.022,30</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.9%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,29 +6852,29 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6884,61 +6884,61 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 24.861,19</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>18.608,52</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-R$ 10.288,22</t>
+          <t>-R$ 9.457,43</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6948,39 +6948,743 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>1725869</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2.488,83</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>R$ 2.488,83</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1726007</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>37.360,00</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>140.684,13</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>-R$ 103.324,13</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-73.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1726008</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>96.656,83</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>203.193,73</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>-R$ 106.536,90</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-52.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1726018</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>43.320,32</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>189.306,13</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>-R$ 145.985,81</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-77.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1726042</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>52.831,30</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>192.548,30</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-R$ 139.717,00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-72.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1726044</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>68.094,35</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>167.292,84</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-R$ 99.198,49</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-59.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1726045</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>59.559,30</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>126.996,75</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-R$ 67.437,45</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-53.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1726057</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>98.316,97</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>196.508,79</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>-R$ 98.191,82</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1726058</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>28.638,24</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>133.354,34</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>-R$ 104.716,10</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-78.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1726324</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2.048,89</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>19.215,26</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-R$ 17.166,37</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-89.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1726332</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>5.722,23</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-R$ 23.174,51</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-80.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>3.252,02</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>11.143,51</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-R$ 7.891,49</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-70.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1727187</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>4.280,60</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>R$ 4.280,60</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1727322</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2.998,50</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>-R$ 8.252,44</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-73.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1727335</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>5.053,73</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>8.079,08</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>-R$ 3.025,35</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-37.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1727808I</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2.562,33</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>8.676,98</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>-R$ 6.114,65</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1728055</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>12.947,91</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>-R$ 29.152,92</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-69.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1728163</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>7.914,69</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>R$ 7.914,69</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1729828</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>914,81</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>-R$ 10.336,13</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-91.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>18.608,52</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>-R$ 10.288,22</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-35.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>1730763</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>4.243,92</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>59.203,65</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>-R$ 54.959,73</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>❌ PREJUÍZO</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
         <is>
           <t>-92.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1730908</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>4.386,39</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>17.270,31</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>-R$ 12.883,92</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-74.6%</t>
         </is>
       </c>
     </row>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>74.647,17</t>
+          <t>87.362,74</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 74.647,17</t>
+          <t>R$ 87.362,74</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 9.859,97</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,76 +2187,76 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>36.411,37</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>70.485,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-R$ 34.074,32</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>36.411,37</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>-R$ 34.074,32</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,118 +2283,118 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1704855</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>92.191,04</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-R$ 113.074,11</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2404,29 +2404,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2436,51 +2436,51 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1704952</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.289,24</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 1.289,24</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,76 +2571,76 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1707182</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>99.018,80</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 99.018,80</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2699,54 +2699,54 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1707502</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3.133,81</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 34.761,58</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2756,51 +2756,51 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2859,12 +2859,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2891,22 +2891,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30.599,33</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 1.198,90</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2916,115 +2916,115 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.198,90</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.153,35</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.153,35</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3211,12 +3211,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3243,86 +3243,86 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,19 +3332,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,140 +3371,140 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3659,12 +3659,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,44 +3947,44 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,44 +4011,44 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>8.854,04</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>-R$ 64.947,55</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.0%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4107,12 +4107,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,12 +4203,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,12 +4235,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,44 +4267,44 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.129,23</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-R$ 12.353,05</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,44 +4331,44 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>1.129,23</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>-R$ 12.353,05</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.6%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,54 +4427,54 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7.890,42</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 1.016,35</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4484,83 +4484,83 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>+14.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>7.890,42</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 1.016,35</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>+14.8%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4587,44 +4587,44 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>18.624,62</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>-R$ 36.398,25</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4843,12 +4843,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4907,44 +4907,44 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4971,44 +4971,44 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,44 +5067,44 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,118 +5131,118 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5252,61 +5252,61 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5316,115 +5316,115 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,44 +5483,44 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,22 +5547,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5572,93 +5572,93 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>24.975,36</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-R$ 20.877,68</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>24.975,36</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-R$ 45.453,71</t>
+          <t>-R$ 20.877,68</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5668,93 +5668,93 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-45.5%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 45.453,71</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5764,51 +5764,51 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5828,29 +5828,29 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5860,157 +5860,157 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6020,29 +6020,29 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6052,61 +6052,61 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>13.736,92</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 41.285,95</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6116,93 +6116,93 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6212,61 +6212,61 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6276,29 +6276,29 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6308,29 +6308,29 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6340,29 +6340,29 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6372,61 +6372,61 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6436,61 +6436,61 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6500,29 +6500,29 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6532,29 +6532,29 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>14.090,54</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>-R$ 191.174,61</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,29 +6564,29 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-93.1%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,29 +6596,29 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6628,51 +6628,51 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6692,61 +6692,61 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-R$ 13.137,83</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6756,29 +6756,29 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6788,29 +6788,29 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>7.181,35</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 52.022,30</t>
+          <t>-R$ 13.137,83</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6820,29 +6820,29 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-87.9%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,29 +6852,29 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>7.181,35</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>-R$ 52.022,30</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6884,29 +6884,29 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-87.9%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6916,29 +6916,29 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6948,61 +6948,61 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>140,91</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 24.861,19</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>37.360,00</t>
+          <t>15.544,67</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-R$ 103.324,13</t>
+          <t>-R$ 9.457,43</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7012,61 +7012,61 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>96.656,83</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>-R$ 106.536,90</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>43.320,32</t>
+          <t>37.360,00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>-R$ 145.985,81</t>
+          <t>-R$ 103.324,13</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7076,29 +7076,29 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-73.4%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>96.656,83</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 106.536,90</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-52.4%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>68.094,35</t>
+          <t>43.320,32</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 99.198,49</t>
+          <t>-R$ 145.985,81</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-77.1%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>59.559,30</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 67.437,45</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,29 +7172,29 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>98.316,97</t>
+          <t>68.094,35</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-R$ 98.191,82</t>
+          <t>-R$ 99.198,49</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7204,29 +7204,29 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-59.3%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>28.638,24</t>
+          <t>59.559,30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-R$ 104.716,10</t>
+          <t>-R$ 67.437,45</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7236,29 +7236,29 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-53.1%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2.048,89</t>
+          <t>98.316,97</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>-R$ 17.166,37</t>
+          <t>-R$ 98.191,82</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7268,29 +7268,29 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-89.3%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>28.638,24</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 104.716,10</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>2.294,20</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 16.921,06</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7332,61 +7332,61 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-88.1%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2.998,50</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 8.252,44</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,93 +7396,93 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>R$ 4.280,60</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.998,50</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 8.252,44</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-73.3%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>8.079,08</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 3.025,35</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,29 +7492,29 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 6.884,13</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7524,19 +7524,19 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-61.2%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7546,12 +7546,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -7563,22 +7563,22 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>8.676,98</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>-R$ 6.114,65</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7588,29 +7588,29 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>18.608,52</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-R$ 10.288,22</t>
+          <t>-R$ 29.152,92</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -7620,69 +7620,165 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>4.243,92</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>-R$ 54.959,73</t>
+          <t>R$ 7.914,69</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-92.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
+          <t>1729828</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>914,81</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>-R$ 10.336,13</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-91.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>18.608,52</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>-R$ 10.288,22</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-35.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>4.243,92</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>-R$ 54.959,73</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-92.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
           <t>1730908</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>4.386,39</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>17.270,31</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>-R$ 12.883,92</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>❌ PREJUÍZO</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
         <is>
           <t>-74.6%</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F230"/>
+  <dimension ref="A1:F249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>53.357,33</t>
+          <t>63.447,09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R$ 53.357,33</t>
+          <t>R$ 63.447,09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1659020</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>64.087,94</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 100,65</t>
+          <t>R$ 64.087,94</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11.953,89</t>
+          <t>246,77</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 11.953,89</t>
+          <t>R$ 246,77</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1663544</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.065,14</t>
+          <t>12.127,29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 1.065,14</t>
+          <t>R$ 12.127,29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 1.065,14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1667134</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.273,55</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 1.273,55</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 1.273,55</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1667819</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>2.550,46</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 2.550,46</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>120.604,17</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 120.604,17</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1355,22 +1355,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>51.640,54</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 51.500,65</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1380,29 +1380,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+36815.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>120.604,17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 51.483,73</t>
+          <t>R$ 120.604,17</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1412,29 +1412,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+36803.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 8,36</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1444,29 +1444,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1515,12 +1515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,76 +1547,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1687268</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.041,79</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 348.950,77</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.3%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1687274</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>44.404,89</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>-R$ 333.587,67</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.3%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1643,12 +1643,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1675,76 +1675,76 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1689263</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>4.336,11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>-R$ 10.929,09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-71.6%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1689264</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>8.697,79</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>-R$ 6.567,41</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,44 +1803,44 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>87.362,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 87.362,74</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,22 +1899,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1924,19 +1924,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,76 +1963,76 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>87.362,74</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 87.362,74</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1702212</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9.859,97</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 9.859,97</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,22 +2091,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2116,19 +2116,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2155,44 +2155,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,44 +2219,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>36.411,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>70.485,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-R$ 34.074,32</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 9.859,97</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,44 +2315,44 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1704855</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>92.191,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-R$ 113.074,11</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2379,54 +2379,54 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>36.411,37</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 34.074,32</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2436,51 +2436,51 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1704952</t>
+          <t>1704477</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.289,24</t>
+          <t>23.120,18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 1.289,24</t>
+          <t>R$ 23.120,18</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,44 +2539,44 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,22 +2603,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2628,83 +2628,83 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1707182</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>99.018,80</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 99.018,80</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2731,76 +2731,76 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1707502</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3.133,81</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-R$ 34.761,58</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2827,44 +2827,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,22 +2923,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30.599,33</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 1.198,90</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2948,61 +2948,61 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3012,19 +3012,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>9.153,35</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 9.153,35</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3147,44 +3147,44 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.198,90</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3211,44 +3211,44 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3275,54 +3275,54 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710220</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>2.270,95</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.270,94</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 0,01</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,19 +3332,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>10.429,60</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 10.429,60</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3371,22 +3371,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>9.751,61</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 9.751,61</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3396,19 +3396,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3435,76 +3435,76 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3531,44 +3531,44 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,54 +3627,54 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>4.381,49</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>-R$ 69.420,10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.1%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3684,19 +3684,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,108 +3723,108 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>-R$ 5.378,25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,12 +3915,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -3979,12 +3979,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,44 +4011,44 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8.854,04</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 64.947,55</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4107,12 +4107,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,44 +4203,44 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>29.639,83</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>-R$ 175.625,32</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.6%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,76 +4331,76 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.129,23</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-R$ 12.353,05</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>10.803,62</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>-R$ 62.997,97</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4491,54 +4491,54 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7.890,42</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 1.016,35</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4548,19 +4548,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>+14.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4587,44 +4587,44 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>18.624,62</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-R$ 36.398,25</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4683,44 +4683,44 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>1.473,94</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>-R$ 12.008,34</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4843,54 +4843,54 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>8.422,88</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 1.548,81</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4900,19 +4900,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4939,76 +4939,76 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>25.018,29</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>-R$ 30.004,58</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,12 +5067,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5099,12 +5099,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5131,44 +5131,44 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5195,12 +5195,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,204 +5227,204 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,44 +5483,44 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,86 +5547,86 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1716557</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>81.673,94</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 138.321,43</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -5636,29 +5636,29 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>24.975,36</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-R$ 20.877,68</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5668,93 +5668,93 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>-R$ 45.453,71</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5764,211 +5764,211 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5995,22 +5995,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>16.304,49</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 29.548,55</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6020,29 +6020,29 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6052,29 +6052,29 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>28.287,18</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 17.565,86</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6084,93 +6084,93 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>13.736,92</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>-R$ 41.285,95</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 45.453,71</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6180,93 +6180,93 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 71.226,89</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6276,29 +6276,29 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6308,29 +6308,29 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6340,29 +6340,29 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6372,29 +6372,29 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>6.946,00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 3.836,30</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6404,51 +6404,51 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6475,22 +6475,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6500,29 +6500,29 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6532,29 +6532,29 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>14.090,54</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 191.174,61</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,29 +6564,29 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-93.1%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>16.536,50</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 38.486,37</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,61 +6596,61 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6660,29 +6660,29 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -6692,19 +6692,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6731,22 +6731,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6756,29 +6756,29 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6788,29 +6788,29 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 13.137,83</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6820,29 +6820,29 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,29 +6852,29 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>7.181,35</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-R$ 52.022,30</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6884,29 +6884,29 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-87.9%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6916,61 +6916,61 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>140,91</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-R$ 24.861,19</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6980,29 +6980,29 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>15.544,67</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-R$ 9.457,43</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7012,61 +7012,61 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>15.490,41</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 189.774,74</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>37.360,00</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>-R$ 103.324,13</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7076,29 +7076,29 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>96.656,83</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 106.536,90</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>43.320,32</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 145.985,81</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,61 +7172,61 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>68.094,35</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-R$ 99.198,49</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>59.559,30</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-R$ 67.437,45</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7236,29 +7236,29 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>98.316,97</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>-R$ 98.191,82</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7268,29 +7268,29 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>28.638,24</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 104.716,10</t>
+          <t>-R$ 13.137,83</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2.294,20</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-R$ 16.921,06</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7332,29 +7332,29 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-88.1%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>8.569,24</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 50.634,41</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7364,29 +7364,29 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,61 +7396,61 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2.998,50</t>
+          <t>146,69</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>-R$ 8.252,44</t>
+          <t>-R$ 24.855,41</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7460,29 +7460,29 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>16.959,62</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 8.042,48</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,93 +7492,93 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>-R$ 6.884,13</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.360,00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 103.324,13</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-73.4%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>96.656,83</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 106.536,90</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7588,29 +7588,29 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-52.4%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>43.320,32</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 145.985,81</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -7620,61 +7620,61 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-77.1%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>68.094,35</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>-R$ 99.198,49</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7684,29 +7684,29 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-59.3%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>18.608,52</t>
+          <t>114.693,62</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>-R$ 10.288,22</t>
+          <t>-R$ 12.303,13</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7716,29 +7716,29 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>4.243,92</t>
+          <t>177.769,55</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>-R$ 54.959,73</t>
+          <t>-R$ 18.739,24</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7748,39 +7748,647 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-92.8%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
+          <t>1726058</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>28.638,24</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>133.354,34</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>-R$ 104.716,10</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-78.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1726324</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2.294,20</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>19.215,26</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>-R$ 16.921,06</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-88.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>1726332</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>5.722,23</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>-R$ 23.174,51</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-80.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>1726890</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>3.252,02</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>11.143,51</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>-R$ 7.891,49</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-70.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1727187</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>4.280,60</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>R$ 4.280,60</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1727322</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2.998,50</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>-R$ 8.252,44</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-73.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1727335</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>5.053,73</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>8.079,08</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>-R$ 3.025,35</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-37.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1727529</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>4.366,81</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>-R$ 6.884,13</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-61.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>1727808I</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2.562,33</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>8.676,98</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>-R$ 6.114,65</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1728055</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>12.947,91</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>-R$ 29.152,92</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-69.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1728163</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>7.914,69</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>R$ 7.914,69</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1728642</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>7.237,16</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>19.215,26</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>-R$ 11.978,10</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>1729668</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1.201,81</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>13.305,24</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>-R$ 12.103,43</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-91.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>1729828</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>914,81</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>-R$ 10.336,13</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-91.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>18.608,52</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-R$ 10.288,22</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-35.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>4.243,92</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-R$ 54.959,73</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-92.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>1730822</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>30.861,26</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>68.930,71</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-R$ 38.069,45</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-55.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
           <t>1730908</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>4.386,39</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>17.270,31</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>-R$ 12.883,92</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>❌ PREJUÍZO</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
         <is>
           <t>-74.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1731653</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>5.940,43</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>R$ 5.940,43</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>107.041,70</t>
+          <t>139.864,72</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-R$ 21.141,15</t>
+          <t>R$ 11.681,87</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>+9.1%</t>
         </is>
       </c>
     </row>
@@ -1611,204 +1611,204 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1687276</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>68.131,64</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>-R$ 309.860,92</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1687278</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>76.729,20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>-R$ 301.263,36</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1689263</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4.336,11</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-R$ 10.929,09</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1689264</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8.697,79</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>-R$ 6.567,41</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1689263</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.336,11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 10.929,09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-71.6%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1689264</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>8.697,79</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>-R$ 6.567,41</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1692415</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>4.712,56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 4.712,56</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,44 +1995,44 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87.362,74</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 87.362,74</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,44 +2091,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1694861</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>3.068,09</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 3.068,09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,44 +2155,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>87.362,74</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 87.362,74</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,44 +2219,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1702212</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9.859,97</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 9.859,97</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,44 +2283,44 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 9.859,97</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2411,44 +2411,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>36.411,37</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>70.485,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>-R$ 34.074,32</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1704477</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>23.120,18</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 23.120,18</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,22 +2539,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1704855</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>92.191,04</t>
+          <t>54.055,77</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-R$ 113.074,11</t>
+          <t>-R$ 16.429,92</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2564,19 +2564,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2603,86 +2603,86 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704477</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>23.120,18</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>R$ 23.120,18</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704802</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>6.266,64</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 52.937,01</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2692,51 +2692,51 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-89.4%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1704952</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.289,24</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>R$ 1.289,24</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2763,86 +2763,86 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2852,19 +2852,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2891,12 +2891,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1707182</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>99.018,80</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 99.018,80</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2955,44 +2955,44 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1707502</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3.133,81</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>-R$ 34.761,58</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3012,19 +3012,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3034,12 +3034,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,76 +3115,76 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30.599,33</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 1.198,90</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3211,44 +3211,44 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1710220</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2.270,95</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2.270,94</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 0,01</t>
+          <t>R$ 1.198,90</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,19 +3332,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3371,44 +3371,44 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>9.751,61</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 9.751,61</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3435,12 +3435,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3467,22 +3467,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710220</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>2.270,95</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.270,94</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 0,01</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3492,19 +3492,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>56,80</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 56,80</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3531,44 +3531,44 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710332</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>223,64</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 223,64</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>10.429,60</t>
+          <t>9.751,61</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 10.429,60</t>
+          <t>R$ 9.751,61</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,54 +3627,54 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1711489</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4.381,49</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-R$ 69.420,10</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>-94.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3684,19 +3684,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3723,54 +3723,54 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3780,51 +3780,51 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>8.104,03</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-R$ 5.378,25</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3851,54 +3851,54 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>4.381,49</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>-R$ 69.420,10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.1%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3908,19 +3908,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -3947,108 +3947,108 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>-R$ 5.378,25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4107,12 +4107,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,44 +4203,44 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1713045</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>29.639,83</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>-R$ 175.625,32</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,44 +4363,44 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>10.803,62</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>-R$ 62.997,97</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,44 +4427,44 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>29.639,83</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>-R$ 175.625,32</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.6%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4491,12 +4491,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4523,12 +4523,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4555,12 +4555,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4587,44 +4587,44 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>10.803,62</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>-R$ 62.997,97</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -4683,44 +4683,44 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.473,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>-R$ 12.008,34</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>-89.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4843,54 +4843,54 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8.422,88</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 1.548,81</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4900,83 +4900,83 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>1.473,94</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>-R$ 12.008,34</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>25.018,29</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>-R$ 30.004,58</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5003,12 +5003,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,54 +5067,54 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>8.422,88</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 1.548,81</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5124,19 +5124,19 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5163,44 +5163,44 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>25.018,29</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>-R$ 30.004,58</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,12 +5227,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -5259,12 +5259,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5323,44 +5323,44 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5387,12 +5387,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5419,12 +5419,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,44 +5483,44 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,470 +5547,470 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1716557</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>81.673,94</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>219.995,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>-R$ 138.321,43</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1716557</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>81.673,94</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 138.321,43</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1718954</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>16.304,49</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-R$ 29.548,55</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6020,83 +6020,83 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>28.287,18</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-R$ 17.565,86</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6123,54 +6123,54 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>-R$ 45.453,71</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6180,19 +6180,19 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2.574,70</t>
+          <t>257,86</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-R$ 71.226,89</t>
+          <t>-R$ 58.945,79</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6244,29 +6244,29 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-99.6%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>16.304,49</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>-R$ 29.548,55</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6276,29 +6276,29 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6308,29 +6308,29 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>28.287,18</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>-R$ 17.565,86</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6340,61 +6340,61 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>6.946,00</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-R$ 3.836,30</t>
+          <t>-R$ 45.453,71</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6404,51 +6404,51 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6475,22 +6475,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 71.226,89</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6500,29 +6500,29 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -6532,29 +6532,29 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,29 +6564,29 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>16.536,50</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 38.486,37</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,61 +6596,61 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>6.946,00</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 3.836,30</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6660,51 +6660,51 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6731,22 +6731,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -6756,29 +6756,29 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -6788,29 +6788,29 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6820,19 +6820,19 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>16.536,50</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 38.486,37</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,61 +6852,61 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6916,93 +6916,93 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7012,29 +7012,29 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>15.490,41</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>-R$ 189.774,74</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -7044,29 +7044,29 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7076,29 +7076,29 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,19 +7172,19 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7211,22 +7211,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7236,29 +7236,29 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -7268,29 +7268,29 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>15.490,41</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 13.137,83</t>
+          <t>-R$ 189.774,74</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1722803</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>1.585,72</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>52.950,36</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 51.364,64</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7332,29 +7332,29 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-97.0%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>8.569,24</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-R$ 50.634,41</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7364,29 +7364,29 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,29 +7396,29 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1723722</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>3.175,84</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>-R$ 7.606,46</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7428,29 +7428,29 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>146,69</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>-R$ 24.855,41</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7460,29 +7460,29 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>16.959,62</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 8.042,48</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,19 +7492,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7531,22 +7531,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>37.360,00</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>-R$ 103.324,13</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7556,29 +7556,29 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>96.656,83</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-R$ 106.536,90</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7588,29 +7588,29 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>43.320,32</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-R$ 145.985,81</t>
+          <t>-R$ 13.137,83</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -7620,29 +7620,29 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -7652,29 +7652,29 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>68.094,35</t>
+          <t>8.569,24</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-R$ 99.198,49</t>
+          <t>-R$ 50.634,41</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7684,29 +7684,29 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>114.693,62</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>-R$ 12.303,13</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7716,29 +7716,29 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>177.769,55</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>-R$ 18.739,24</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7748,29 +7748,29 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>28.638,24</t>
+          <t>146,69</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>-R$ 104.716,10</t>
+          <t>-R$ 24.855,41</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7780,29 +7780,29 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2.294,20</t>
+          <t>16.959,62</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>-R$ 16.921,06</t>
+          <t>-R$ 8.042,48</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -7812,61 +7812,61 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-88.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>37.360,00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 103.324,13</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -7876,61 +7876,61 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-73.4%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>96.656,83</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 106.536,90</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-52.4%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2.998,50</t>
+          <t>43.320,32</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-R$ 8.252,44</t>
+          <t>-R$ 145.985,81</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7940,29 +7940,29 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-77.1%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -7972,29 +7972,29 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>163.324,35</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-R$ 6.884,13</t>
+          <t>-R$ 3.968,49</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8004,61 +8004,61 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>114.693,62</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 12.303,13</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>177.769,55</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 18.739,24</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>103.529,88</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 29.824,46</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8100,61 +8100,61 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-22.4%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>2.294,20</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 16.921,06</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.1%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1728642</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>7.237,16</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-R$ 11.978,10</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -8164,29 +8164,29 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-62.3%</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1729668</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>1.201,81</t>
+          <t>24.645,05</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-R$ 12.103,43</t>
+          <t>-R$ 17.455,78</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8196,29 +8196,29 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>-41.5%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8228,93 +8228,93 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>18.608,52</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>-R$ 10.288,22</t>
+          <t>R$ 4.280,60</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1727287</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>4.243,92</t>
+          <t>489,21</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>-R$ 54.959,73</t>
+          <t>R$ 489,21</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>-92.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>30.861,26</t>
+          <t>3.146,66</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>68.930,71</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>-R$ 38.069,45</t>
+          <t>-R$ 8.104,28</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8324,29 +8324,29 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>4.386,39</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>17.270,31</t>
+          <t>8.079,08</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>-R$ 12.883,92</t>
+          <t>-R$ 3.025,35</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8356,37 +8356,485 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
+          <t>1727529</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>4.366,81</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-R$ 6.884,13</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-61.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>1727778</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>3.846,49</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>R$ 3.846,49</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>1727808</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>1727808I</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2.562,33</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>8.676,98</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>-R$ 6.114,65</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-70.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1728055</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>12.947,91</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>-R$ 29.152,92</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-69.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>1728163</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>7.914,69</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>R$ 7.914,69</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>1728642</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>7.237,16</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>19.215,26</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>-R$ 11.978,10</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-62.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>1729668</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1.201,81</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>13.305,24</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>-R$ 12.103,43</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-91.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>1729828</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>914,81</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>-R$ 10.336,13</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-91.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>21.764,18</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>-R$ 7.132,56</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-24.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>1730270</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>10.340,91</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>-R$ 31.759,92</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-75.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>4.973,33</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>-R$ 54.230,32</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>-91.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>1730822</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>30.861,26</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>68.930,71</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>-R$ 38.069,45</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>-55.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>1730908</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>4.386,39</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>17.270,31</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>-R$ 12.883,92</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-74.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
           <t>1731653</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>5.940,43</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
         <is>
           <t>R$ 5.940,43</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F263"/>
+  <dimension ref="A1:F267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,12 +715,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1595636</t>
+          <t>1590713</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>760,40</t>
+          <t>1.503,25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>R$ 760,40</t>
+          <t>R$ 1.503,25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1641139I</t>
+          <t>1595636</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>760,40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 760,40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1648254</t>
+          <t>1641139I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -811,12 +811,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1657710</t>
+          <t>1648254</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>59.714,14</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R$ 59.714,14</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -843,12 +843,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1657713</t>
+          <t>1657710</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>83.267,14</t>
+          <t>59.714,14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R$ 83.267,14</t>
+          <t>R$ 59.714,14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,12 +875,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1658452</t>
+          <t>1657713</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.792,10</t>
+          <t>83.267,14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>R$ 7.792,10</t>
+          <t>R$ 83.267,14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,12 +907,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1658892</t>
+          <t>1658452</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40.789,42</t>
+          <t>7.792,10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>R$ 40.789,42</t>
+          <t>R$ 7.792,10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,12 +939,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1659019</t>
+          <t>1658892</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9.678,68</t>
+          <t>40.789,42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>R$ 9.678,68</t>
+          <t>R$ 40.789,42</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1659020</t>
+          <t>1659019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>64.087,94</t>
+          <t>9.678,68</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>R$ 64.087,94</t>
+          <t>R$ 9.678,68</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1660062C</t>
+          <t>1659020</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>246,77</t>
+          <t>64.087,94</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>R$ 246,77</t>
+          <t>R$ 64.087,94</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,12 +1035,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1660062I</t>
+          <t>1660062C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12.127,29</t>
+          <t>246,77</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>R$ 12.127,29</t>
+          <t>R$ 246,77</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,12 +1067,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1663544</t>
+          <t>1660062I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.065,14</t>
+          <t>12.127,29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>R$ 1.065,14</t>
+          <t>R$ 12.127,29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,12 +1099,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1663556</t>
+          <t>1663544</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2.470,38</t>
+          <t>1.065,14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>R$ 2.470,38</t>
+          <t>R$ 1.065,14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,12 +1131,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1667134</t>
+          <t>1663556</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.273,55</t>
+          <t>2.470,38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>R$ 1.273,55</t>
+          <t>R$ 2.470,38</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1667141</t>
+          <t>1667134</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>661,89</t>
+          <t>1.273,55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R$ 661,89</t>
+          <t>R$ 1.273,55</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1667593</t>
+          <t>1667141</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>661,89</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 661,89</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1227,12 +1227,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1667819</t>
+          <t>1667593</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2.550,46</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>R$ 2.550,46</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1259,12 +1259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1671139I</t>
+          <t>1667819</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6.138,54</t>
+          <t>2.550,46</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>R$ 6.138,54</t>
+          <t>R$ 2.550,46</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1675032C</t>
+          <t>1671139I</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>23,99</t>
+          <t>6.138,54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>R$ 23,99</t>
+          <t>R$ 6.138,54</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,12 +1323,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1675032I</t>
+          <t>1675032C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>222.884,15</t>
+          <t>23,99</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>R$ 222.884,15</t>
+          <t>R$ 23,99</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1355,12 +1355,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1675389</t>
+          <t>1675032I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>389,52</t>
+          <t>222.884,15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>R$ 389,52</t>
+          <t>R$ 222.884,15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1387,12 +1387,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1676605</t>
+          <t>1675389</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>120.604,17</t>
+          <t>389,52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R$ 120.604,17</t>
+          <t>R$ 389,52</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1419,22 +1419,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1677314</t>
+          <t>1676605</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>51.640,54</t>
+          <t>120.604,17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>139,89</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 51.500,65</t>
+          <t>R$ 120.604,17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1444,19 +1444,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+36815.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1677316</t>
+          <t>1677314</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>51.623,62</t>
+          <t>51.640,54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>R$ 51.483,73</t>
+          <t>R$ 51.500,65</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1476,29 +1476,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+36803.0%</t>
+          <t>+36815.1%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1682195</t>
+          <t>1677316</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8,36</t>
+          <t>51.623,62</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>139,89</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>R$ 8,36</t>
+          <t>R$ 51.483,73</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1508,19 +1508,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36803.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1683861I</t>
+          <t>1682195</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20.224,44</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>R$ 20.224,44</t>
+          <t>R$ 8,36</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1547,44 +1547,44 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1687268</t>
+          <t>1683861I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>29.041,79</t>
+          <t>20.224,44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>377.992,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-R$ 348.950,77</t>
+          <t>R$ 20.224,44</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-92.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1687274</t>
+          <t>1687268</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>44.404,89</t>
+          <t>29.041,79</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-R$ 333.587,67</t>
+          <t>-R$ 348.950,77</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1604,19 +1604,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-88.3%</t>
+          <t>-92.3%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1687276</t>
+          <t>1687274</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>68.131,64</t>
+          <t>44.404,89</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-R$ 309.860,92</t>
+          <t>-R$ 333.587,67</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1636,19 +1636,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-82.0%</t>
+          <t>-88.3%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1687278</t>
+          <t>1687276</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>76.729,20</t>
+          <t>68.131,64</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-R$ 301.263,36</t>
+          <t>-R$ 309.860,92</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1668,51 +1668,51 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1687278</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>76.729,20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>-R$ 301.263,36</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1739,44 +1739,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1689263</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4.336,11</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-R$ 10.929,09</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1689264</t>
+          <t>1689263</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8.697,79</t>
+          <t>4.336,11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-R$ 6.567,41</t>
+          <t>-R$ 10.929,09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1796,51 +1796,51 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>-71.6%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1689264</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.697,79</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 6.567,41</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1867,12 +1867,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1692415</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4.712,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 4.712,56</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692415</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>4.712,56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 4.712,56</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,76 +2091,76 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1694861</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3.068,09</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>R$ 3.068,09</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694861</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>87.362,74</t>
+          <t>3.068,09</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 87.362,74</t>
+          <t>R$ 3.068,09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,12 +2187,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>87.362,74</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 87.362,74</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,22 +2219,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2244,29 +2244,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2276,83 +2276,83 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1702212</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9.859,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 9.859,97</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,12 +2411,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 9.859,97</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2475,12 +2475,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,76 +2539,76 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>54.055,77</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>70.485,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>-R$ 16.429,92</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>54.055,77</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>-R$ 16.429,92</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1704477</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>23.120,18</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 23.120,18</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704477</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>23.120,18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>R$ 23.120,18</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,54 +2667,54 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1704802</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6.266,64</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-R$ 52.937,01</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>-89.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1704855</t>
+          <t>1704802</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>92.191,04</t>
+          <t>6.266,64</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 113.074,11</t>
+          <t>-R$ 52.937,01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2724,93 +2724,93 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>-89.4%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2852,51 +2852,51 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1704952</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.289,24</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>R$ 1.289,24</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2923,12 +2923,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2955,12 +2955,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2987,76 +2987,76 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1707182</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>99.018,80</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 99.018,80</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,54 +3115,54 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1707502</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>3.133,81</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-R$ 34.761,58</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3172,51 +3172,51 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3307,22 +3307,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30.599,33</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 1.198,90</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3332,115 +3332,115 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.198,90</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3467,54 +3467,54 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1710220</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2.270,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2.270,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 0,01</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1710287C</t>
+          <t>1710220</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>56,80</t>
+          <t>2.270,95</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.270,94</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 56,80</t>
+          <t>R$ 0,01</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3524,19 +3524,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>56,80</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 56,80</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1710287I</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>223,64</t>
+          <t>8.740,43</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 223,64</t>
+          <t>R$ 8.740,43</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>9.751,61</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 9.751,61</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3627,12 +3627,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710332</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>223,64</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 223,64</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3659,12 +3659,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>9.751,61</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 9.751,61</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3755,44 +3755,44 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3819,86 +3819,86 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10.429,60</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>R$ 10.429,60</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1711489</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4.381,49</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-R$ 69.420,10</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-94.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3908,115 +3908,115 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>4.381,49</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>-R$ 69.420,10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.1%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8.104,03</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 5.378,25</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4036,83 +4036,83 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>-R$ 5.378,25</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4171,12 +4171,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4203,12 +4203,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4235,12 +4235,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,44 +4427,44 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1713045</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>29.639,83</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>-R$ 175.625,32</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4491,44 +4491,44 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>29.639,83</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>-R$ 175.625,32</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.6%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4555,12 +4555,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>9.773,21</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>R$ 9.773,21</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4587,44 +4587,44 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>10.803,62</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-R$ 62.997,97</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4651,44 +4651,44 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>10.803,62</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>-R$ 62.997,97</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4843,12 +4843,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -4907,44 +4907,44 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.473,94</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-R$ 12.008,34</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>-89.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4971,44 +4971,44 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>1.473,94</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>-R$ 12.008,34</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,54 +5067,54 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>8.422,88</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 1.548,81</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5124,83 +5124,83 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>25.018,29</t>
+          <t>8.422,88</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-R$ 30.004,58</t>
+          <t>R$ 1.548,81</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,44 +5227,44 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>25.018,29</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>-R$ 30.004,58</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5323,12 +5323,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5355,12 +5355,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5387,12 +5387,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5419,12 +5419,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5515,12 +5515,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,44 +5547,44 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5611,44 +5611,44 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5707,44 +5707,44 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -5771,118 +5771,118 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1716557</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>81.673,94</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>219.995,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>-R$ 138.321,43</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>2.970,68</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>R$ 2.970,68</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1716557</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>81.673,94</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>-R$ 138.321,43</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5892,29 +5892,29 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5924,61 +5924,61 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -5988,115 +5988,115 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6123,12 +6123,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6155,44 +6155,44 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1718951</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>257,86</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-R$ 58.945,79</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6244,61 +6244,61 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-99.6%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1718954</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>16.304,49</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>-R$ 29.548,55</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>257,86</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>-R$ 58.945,79</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6308,19 +6308,19 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-99.6%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>28.287,18</t>
+          <t>16.304,49</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 17.565,86</t>
+          <t>-R$ 29.548,55</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6340,61 +6340,61 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>28.287,18</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-R$ 45.453,71</t>
+          <t>-R$ 17.565,86</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6404,93 +6404,93 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>9.937,52</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 45.453,71</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.1%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2.574,70</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 71.226,89</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6500,61 +6500,61 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>-R$ 71.226,89</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,19 +6564,19 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -6596,29 +6596,29 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6628,29 +6628,29 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>6.946,00</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 3.836,30</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6660,157 +6660,157 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>6.946,00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 3.836,30</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6820,29 +6820,29 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>16.536,50</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 38.486,37</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,61 +6852,61 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>16.536,50</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 38.486,37</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -6916,93 +6916,93 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7012,61 +7012,61 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7076,29 +7076,29 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7108,29 +7108,29 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,61 +7172,61 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7236,61 +7236,61 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>15.490,41</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 189.774,74</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1722803</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>1.585,72</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>52.950,36</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-R$ 51.364,64</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7332,29 +7332,29 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-97.0%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>15.490,41</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>-R$ 189.774,74</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7364,29 +7364,29 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1722803</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>1.585,72</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>52.950,36</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>-R$ 51.364,64</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,29 +7396,29 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-97.0%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1723722</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>3.175,84</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>-R$ 7.606,46</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -7428,19 +7428,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7460,29 +7460,29 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1723722</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>3.175,84</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 7.606,46</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,61 +7492,61 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1724053</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>3.088,86</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 148.406,48</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7556,29 +7556,29 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-98.0%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7588,61 +7588,61 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>-R$ 13.137,83</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -7652,29 +7652,29 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>8.569,24</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-R$ 50.634,41</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7684,29 +7684,29 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>6.077,43</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 13.137,83</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7716,29 +7716,29 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-68.4%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7748,29 +7748,29 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>146,69</t>
+          <t>8.569,24</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>-R$ 24.855,41</t>
+          <t>-R$ 50.634,41</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7780,29 +7780,29 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1724663</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>16.959,62</t>
+          <t>3.091,28</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>-R$ 8.042,48</t>
+          <t>-R$ 19.096,69</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -7812,61 +7812,61 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-86.1%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>37.360,00</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>-R$ 103.324,13</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -7876,29 +7876,29 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>96.656,83</t>
+          <t>146,69</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-R$ 106.536,90</t>
+          <t>-R$ 24.855,41</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -7908,29 +7908,29 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>43.320,32</t>
+          <t>16.959,62</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-R$ 145.985,81</t>
+          <t>-R$ 8.042,48</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7940,61 +7940,61 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>163.324,35</t>
+          <t>37.360,00</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-R$ 3.968,49</t>
+          <t>-R$ 103.324,13</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8004,29 +8004,29 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-73.4%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>114.693,62</t>
+          <t>96.656,83</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-R$ 12.303,13</t>
+          <t>-R$ 106.536,90</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-52.4%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>177.769,55</t>
+          <t>43.320,32</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-R$ 18.739,24</t>
+          <t>-R$ 145.985,81</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-77.1%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>103.529,88</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-R$ 29.824,46</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8100,29 +8100,29 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2.294,20</t>
+          <t>163.324,35</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-R$ 16.921,06</t>
+          <t>-R$ 3.968,49</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8132,29 +8132,29 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-88.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>114.693,62</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 12.303,13</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -8164,29 +8164,29 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1726496</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>24.645,05</t>
+          <t>177.769,55</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-R$ 17.455,78</t>
+          <t>-R$ 18.739,24</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8196,29 +8196,29 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>103.529,88</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 29.824,46</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8228,93 +8228,93 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-22.4%</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>2.294,20</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 16.921,06</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-88.1%</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1727287</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>489,21</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>R$ 489,21</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>3.146,66</t>
+          <t>24.645,05</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>-R$ 8.104,28</t>
+          <t>-R$ 17.455,78</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8324,29 +8324,29 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-41.5%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8356,51 +8356,51 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>-R$ 6.884,13</t>
+          <t>R$ 4.280,60</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1727778</t>
+          <t>1727287</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>3.846,49</t>
+          <t>489,21</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>R$ 3.846,49</t>
+          <t>R$ 489,21</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -8427,54 +8427,54 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3.146,66</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 8.104,28</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>8.079,08</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>-R$ 3.025,35</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 6.884,13</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8516,19 +8516,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-61.2%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1727778</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>3.846,49</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>R$ 3.846,49</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -8555,54 +8555,54 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1728642</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7.237,16</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>-R$ 11.978,10</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>-62.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1729668</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>1.201,81</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>8.676,98</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>-R$ 12.103,43</t>
+          <t>-R$ 6.114,65</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8612,29 +8612,29 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>-R$ 29.152,92</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8644,61 +8644,61 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>21.764,18</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>-R$ 7.132,56</t>
+          <t>R$ 7.914,69</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1730270</t>
+          <t>1728642</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>10.340,91</t>
+          <t>7.237,16</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-R$ 31.759,92</t>
+          <t>-R$ 11.978,10</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8708,29 +8708,29 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-62.3%</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1729668</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>4.973,33</t>
+          <t>1.201,81</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-R$ 54.230,32</t>
+          <t>-R$ 12.103,43</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -8740,29 +8740,29 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>-91.0%</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1729828</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>30.861,26</t>
+          <t>914,81</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>68.930,71</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>-R$ 38.069,45</t>
+          <t>-R$ 10.336,13</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -8772,29 +8772,29 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1730222</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>4.386,39</t>
+          <t>21.764,18</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>17.270,31</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>-R$ 12.883,92</t>
+          <t>-R$ 7.132,56</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8804,37 +8804,165 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-24.7%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
+          <t>1730270</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>10.340,91</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>-R$ 31.759,92</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-75.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>4.973,33</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>-R$ 54.230,32</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-91.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1730822</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>30.861,26</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>68.930,71</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-R$ 38.069,45</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-55.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>1730908</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>4.386,39</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>17.270,31</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-R$ 12.883,92</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-74.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
           <t>1731653</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>5.940,43</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
         <is>
           <t>R$ 5.940,43</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/analise_financeira.xlsx
+++ b/analise_financeira.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>120.604,17</t>
+          <t>127.656,50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R$ 120.604,17</t>
+          <t>R$ 127.656,50</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1579,76 +1579,76 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1687268</t>
+          <t>1686607C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>29.041,79</t>
+          <t>21,97</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>377.992,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-R$ 348.950,77</t>
+          <t>R$ 21,97</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-92.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1687274</t>
+          <t>1686607I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>44.404,89</t>
+          <t>1.195,62</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>377.992,56</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-R$ 333.587,67</t>
+          <t>R$ 1.195,62</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-88.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1687276</t>
+          <t>1687268</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>68.131,64</t>
+          <t>29.041,79</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>-R$ 309.860,92</t>
+          <t>-R$ 348.950,77</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1668,19 +1668,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-82.0%</t>
+          <t>-92.3%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1687278</t>
+          <t>1687274</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>76.729,20</t>
+          <t>44.404,89</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>-R$ 301.263,36</t>
+          <t>-R$ 333.587,67</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1700,211 +1700,211 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-88.3%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1688115C</t>
+          <t>1687276</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13,01</t>
+          <t>68.131,64</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>R$ 13,01</t>
+          <t>-R$ 309.860,92</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-82.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1688115I</t>
+          <t>1687278</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21.423,48</t>
+          <t>76.729,20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>377.992,56</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R$ 21.423,48</t>
+          <t>-R$ 301.263,36</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1689263</t>
+          <t>1688115C</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4.336,11</t>
+          <t>13,01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-R$ 10.929,09</t>
+          <t>R$ 13,01</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1689264</t>
+          <t>1688115I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8.697,79</t>
+          <t>21.423,48</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>15.265,20</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>-R$ 6.567,41</t>
+          <t>R$ 21.423,48</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-43.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1691380</t>
+          <t>1689263</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.336,11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-R$ 10.929,09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-71.6%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1691390</t>
+          <t>1689264</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>457,30</t>
+          <t>8.697,79</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>15.265,20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R$ 457,30</t>
+          <t>-R$ 6.567,41</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-43.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1691534</t>
+          <t>1691380</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21.331,31</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R$ 21.331,31</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1692174</t>
+          <t>1691390</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>457,30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 457,30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1692415</t>
+          <t>1691534</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4.712,56</t>
+          <t>21.331,31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>R$ 4.712,56</t>
+          <t>R$ 21.331,31</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,12 +1995,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1692636</t>
+          <t>1692174</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19.387,05</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>R$ 19.387,05</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1693027</t>
+          <t>1692415</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.215,91</t>
+          <t>4.712,56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R$ 2.215,91</t>
+          <t>R$ 4.712,56</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1694202</t>
+          <t>1692636</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4.490,43</t>
+          <t>19.387,05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>R$ 4.490,43</t>
+          <t>R$ 19.387,05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1694258</t>
+          <t>1693027</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>127.751,38</t>
+          <t>2.215,91</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>R$ 127.751,38</t>
+          <t>R$ 2.215,91</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,44 +2123,44 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1694841</t>
+          <t>1694202</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5.640,24</t>
+          <t>4.490,43</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>-R$ 19.361,86</t>
+          <t>R$ 4.490,43</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1694861</t>
+          <t>1694258</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3.068,09</t>
+          <t>127.751,38</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>R$ 3.068,09</t>
+          <t>R$ 127.751,38</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,44 +2187,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1695716</t>
+          <t>1694841</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>87.362,74</t>
+          <t>5.640,24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R$ 87.362,74</t>
+          <t>-R$ 19.361,86</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1698047</t>
+          <t>1694861</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.449,89</t>
+          <t>3.068,09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R$ 2.449,89</t>
+          <t>R$ 3.068,09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2251,22 +2251,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1698056</t>
+          <t>1695716</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9.658,39</t>
+          <t>87.362,74</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7.099,38</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>R$ 2.559,01</t>
+          <t>R$ 87.362,74</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2276,93 +2276,93 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1698781</t>
+          <t>1697912</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>914,56</t>
+          <t>1.318,82</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R$ 914,56</t>
+          <t>-R$ 11.986,42</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.1%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1699516</t>
+          <t>1698047</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.676,47</t>
+          <t>2.449,89</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-R$ 26.474,31</t>
+          <t>R$ 2.449,89</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-87.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1700852</t>
+          <t>1698056</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12.509,24</t>
+          <t>9.658,39</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.099,38</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>R$ 12.509,24</t>
+          <t>R$ 2.559,01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2372,19 +2372,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+36.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1702127</t>
+          <t>1698781</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>914,56</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 914,56</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2411,44 +2411,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1702212</t>
+          <t>1699516</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9.859,97</t>
+          <t>3.676,47</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 9.859,97</t>
+          <t>-R$ 26.474,31</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.8%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1702640</t>
+          <t>1700852</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2.963,92</t>
+          <t>12.509,24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 2.963,92</t>
+          <t>R$ 12.509,24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1702776C</t>
+          <t>1702127</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2507,12 +2507,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1702776I</t>
+          <t>1702212</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18.098,87</t>
+          <t>9.859,97</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>R$ 18.098,87</t>
+          <t>R$ 9.859,97</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1703223</t>
+          <t>1702640</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19.640,49</t>
+          <t>2.963,92</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>R$ 19.640,49</t>
+          <t>R$ 2.963,92</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2571,44 +2571,44 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1704074</t>
+          <t>1702776C</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>54.055,77</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>70.485,69</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>-R$ 16.429,92</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1704476</t>
+          <t>1702776I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>31.763,92</t>
+          <t>18.098,87</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>R$ 31.763,92</t>
+          <t>R$ 18.098,87</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1704477</t>
+          <t>1703223</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>23.120,18</t>
+          <t>19.640,49</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 23.120,18</t>
+          <t>R$ 19.640,49</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2667,108 +2667,108 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1704525</t>
+          <t>1704074</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15.452,25</t>
+          <t>54.055,77</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>70.485,69</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 15.452,25</t>
+          <t>-R$ 16.429,92</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1704802</t>
+          <t>1704476</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6.266,64</t>
+          <t>31.763,92</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-R$ 52.937,01</t>
+          <t>R$ 31.763,92</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>-89.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1704855</t>
+          <t>1704477</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>92.191,04</t>
+          <t>23.120,18</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>-R$ 113.074,11</t>
+          <t>R$ 23.120,18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-55.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1704867</t>
+          <t>1704525</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23.915,48</t>
+          <t>15.452,25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>R$ 23.915,48</t>
+          <t>R$ 15.452,25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2795,22 +2795,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1704877</t>
+          <t>1704802</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>159.866,42</t>
+          <t>6.266,64</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>164.923,77</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>-R$ 5.057,35</t>
+          <t>-R$ 52.937,01</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-89.4%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1704891</t>
+          <t>1704855</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>142.006,76</t>
+          <t>92.191,04</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>163.376,34</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>-R$ 21.369,58</t>
+          <t>-R$ 113.074,11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2852,147 +2852,147 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-55.1%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1704920</t>
+          <t>1704867</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>58.137,43</t>
+          <t>23.915,48</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>132.320,57</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>-R$ 74.183,14</t>
+          <t>R$ 23.915,48</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-56.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1704952</t>
+          <t>1704877</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.289,24</t>
+          <t>159.866,42</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>164.923,77</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 1.289,24</t>
+          <t>-R$ 5.057,35</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.1%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1704953</t>
+          <t>1704891</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>9.260,98</t>
+          <t>142.006,76</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>163.376,34</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 9.260,98</t>
+          <t>-R$ 21.369,58</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13.1%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1704964</t>
+          <t>1704920</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.692,23</t>
+          <t>58.137,43</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>132.320,57</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>R$ 2.692,23</t>
+          <t>-R$ 74.183,14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1704968</t>
+          <t>1704952</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.808,15</t>
+          <t>1.289,24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>R$ 2.808,15</t>
+          <t>R$ 1.289,24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3019,44 +3019,44 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1705074</t>
+          <t>1704953</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>150.312,87</t>
+          <t>9.260,98</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>-R$ 231.969,87</t>
+          <t>R$ 9.260,98</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1705802I</t>
+          <t>1704964</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.692,23</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 2.692,23</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3083,12 +3083,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1707174</t>
+          <t>1704968</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.924,94</t>
+          <t>2.808,15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R$ 1.924,94</t>
+          <t>R$ 2.808,15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3115,108 +3115,108 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1707182</t>
+          <t>1705074</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>99.018,80</t>
+          <t>150.312,87</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>R$ 99.018,80</t>
+          <t>-R$ 231.969,87</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-60.7%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1707502</t>
+          <t>1705802I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3.133,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>37.895,39</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-R$ 34.761,58</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1707817</t>
+          <t>1706284</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>138.680,75</t>
+          <t>2.060,27</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>382.282,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-R$ 243.601,99</t>
+          <t>R$ 2.060,27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>-63.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1708066</t>
+          <t>1707174</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3.419,06</t>
+          <t>1.924,94</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>R$ 3.419,06</t>
+          <t>R$ 1.924,94</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3243,12 +3243,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1708877</t>
+          <t>1707182</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>3,54</t>
+          <t>99.018,80</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R$ 3,54</t>
+          <t>R$ 99.018,80</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3275,86 +3275,86 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1708877I</t>
+          <t>1707502</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2.132,72</t>
+          <t>3.133,81</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>37.895,39</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>R$ 2.132,72</t>
+          <t>-R$ 34.761,58</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-91.7%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1708906</t>
+          <t>1707817</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7.584,06</t>
+          <t>138.680,75</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>382.282,74</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>R$ 7.584,06</t>
+          <t>-R$ 243.601,99</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.7%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1708908</t>
+          <t>1708066</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30.599,33</t>
+          <t>3.419,06</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>29.400,43</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>R$ 1.198,90</t>
+          <t>R$ 3.419,06</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3364,19 +3364,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1709419</t>
+          <t>1708877</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 3,54</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3403,44 +3403,44 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1709486</t>
+          <t>1708877I</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>6.291,40</t>
+          <t>2.132,72</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>47.063,85</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-R$ 40.772,45</t>
+          <t>R$ 2.132,72</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>-86.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1709995</t>
+          <t>1708906</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2.410,16</t>
+          <t>7.584,06</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>R$ 2.410,16</t>
+          <t>R$ 7.584,06</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3467,108 +3467,108 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1710116</t>
+          <t>1708908</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.599,33</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>29.400,43</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 1.198,90</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.1%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1710220</t>
+          <t>1709419</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2.270,95</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2.270,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>R$ 0,01</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>+0.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1710287C</t>
+          <t>1709486</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>56,80</t>
+          <t>6.291,40</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>47.063,85</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>R$ 56,80</t>
+          <t>-R$ 40.772,45</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-86.6%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1710287I</t>
+          <t>1709995</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8.740,43</t>
+          <t>2.410,16</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 8.740,43</t>
+          <t>R$ 2.410,16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3595,12 +3595,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1710329</t>
+          <t>1710116</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>24.211,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 24.211,86</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3627,22 +3627,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1710332</t>
+          <t>1710220</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>223,64</t>
+          <t>2.270,95</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.270,94</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>R$ 223,64</t>
+          <t>R$ 0,01</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -3652,19 +3652,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.0%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1710735</t>
+          <t>1710287C</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>9.751,61</t>
+          <t>56,80</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>R$ 9.751,61</t>
+          <t>R$ 56,80</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -3691,12 +3691,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1710736</t>
+          <t>1710287I</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.740,43</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 8.740,43</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1710937</t>
+          <t>1710329</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4.234,81</t>
+          <t>24.211,86</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>R$ 4.234,81</t>
+          <t>R$ 24.211,86</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3755,12 +3755,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1710975</t>
+          <t>1710332</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>913,41</t>
+          <t>223,64</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>R$ 913,41</t>
+          <t>R$ 223,64</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1711110</t>
+          <t>1710735</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>9.751,61</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 9.751,61</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3819,44 +3819,44 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1711378</t>
+          <t>1710736</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>9.934,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>10.727,58</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-R$ 793,48</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1711384</t>
+          <t>1710937</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2.250,33</t>
+          <t>4.234,81</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>R$ 2.250,33</t>
+          <t>R$ 4.234,81</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1711454</t>
+          <t>1710975</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>10.429,60</t>
+          <t>913,41</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>R$ 10.429,60</t>
+          <t>R$ 913,41</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3915,76 +3915,76 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1711489</t>
+          <t>1711110</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4.381,49</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-R$ 69.420,10</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-94.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1711507</t>
+          <t>1711378</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>14.415,50</t>
+          <t>9.934,10</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>13.503,20</t>
+          <t>10.727,58</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>R$ 912,30</t>
+          <t>-R$ 793,48</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1711525</t>
+          <t>1711384</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2.125,35</t>
+          <t>2.250,33</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>R$ 2.125,35</t>
+          <t>R$ 2.250,33</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4011,54 +4011,54 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1711629</t>
+          <t>1711454</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4.201,07</t>
+          <t>10.429,60</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>-R$ 9.281,21</t>
+          <t>R$ 10.429,60</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-68.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1711775</t>
+          <t>1711489</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.932,93</t>
+          <t>4.381,49</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2.356,20</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>-R$ 423,27</t>
+          <t>-R$ 69.420,10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4068,51 +4068,51 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-94.1%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1711788</t>
+          <t>1711507</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>8.104,03</t>
+          <t>14.415,50</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>13.503,20</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-R$ 5.378,25</t>
+          <t>R$ 912,30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>+6.8%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1712530</t>
+          <t>1711525</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6.922,75</t>
+          <t>2.125,35</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 6.922,75</t>
+          <t>R$ 2.125,35</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4139,108 +4139,108 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1712531</t>
+          <t>1711629</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5.019,99</t>
+          <t>4.201,07</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>R$ 5.019,99</t>
+          <t>-R$ 9.281,21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1712533</t>
+          <t>1711775</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2.680,86</t>
+          <t>1.932,93</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2.356,20</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>R$ 2.680,86</t>
+          <t>-R$ 423,27</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-18.0%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1712538</t>
+          <t>1711788</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3.955,41</t>
+          <t>8.104,03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>R$ 3.955,41</t>
+          <t>-R$ 5.378,25</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-39.9%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1712547</t>
+          <t>1712530</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7.069,45</t>
+          <t>6.922,75</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 7.069,45</t>
+          <t>R$ 6.922,75</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4267,12 +4267,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1712550</t>
+          <t>1712531</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5.007,08</t>
+          <t>5.019,99</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>R$ 5.007,08</t>
+          <t>R$ 5.019,99</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1712624</t>
+          <t>1712533</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3.073,90</t>
+          <t>2.680,86</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>R$ 3.073,90</t>
+          <t>R$ 2.680,86</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4331,12 +4331,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1712766</t>
+          <t>1712538</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>705,45</t>
+          <t>3.955,41</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>R$ 705,45</t>
+          <t>R$ 3.955,41</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1712957</t>
+          <t>1712547</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2.222,83</t>
+          <t>7.069,45</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 2.222,83</t>
+          <t>R$ 7.069,45</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4395,12 +4395,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1712963I</t>
+          <t>1712550</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12.285,61</t>
+          <t>5.007,08</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>R$ 12.285,61</t>
+          <t>R$ 5.007,08</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4427,12 +4427,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1713044C</t>
+          <t>1712624</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21,11</t>
+          <t>3.073,90</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>R$ 21,11</t>
+          <t>R$ 3.073,90</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1713044I</t>
+          <t>1712766</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.528,53</t>
+          <t>705,45</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>R$ 1.528,53</t>
+          <t>R$ 705,45</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4491,44 +4491,44 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1713045</t>
+          <t>1712957</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>29.639,83</t>
+          <t>2.222,83</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>-R$ 175.625,32</t>
+          <t>R$ 2.222,83</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>-85.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1713221</t>
+          <t>1712963I</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>18.794,09</t>
+          <t>12.285,61</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>R$ 18.794,09</t>
+          <t>R$ 12.285,61</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4555,12 +4555,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1713223</t>
+          <t>1713044C</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9.773,21</t>
+          <t>21,11</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>R$ 9.773,21</t>
+          <t>R$ 21,11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4587,12 +4587,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1713226</t>
+          <t>1713044I</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3.287,04</t>
+          <t>1.528,53</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>R$ 3.287,04</t>
+          <t>R$ 1.528,53</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4619,76 +4619,76 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1713240</t>
+          <t>1713045</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5.108,11</t>
+          <t>29.639,83</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>R$ 5.108,11</t>
+          <t>-R$ 175.625,32</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.6%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1713260</t>
+          <t>1713221</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>10.803,62</t>
+          <t>18.794,09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>-R$ 62.997,97</t>
+          <t>R$ 18.794,09</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-85.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1713262</t>
+          <t>1713223</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2.675,61</t>
+          <t>13.438,83</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>R$ 2.675,61</t>
+          <t>R$ 13.438,83</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1713351</t>
+          <t>1713226</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>622,97</t>
+          <t>3.287,04</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 622,97</t>
+          <t>R$ 3.287,04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -4747,12 +4747,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1713435I</t>
+          <t>1713240</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>5.108,11</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 5.108,11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4779,44 +4779,44 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1713626</t>
+          <t>1713260</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>161,42</t>
+          <t>10.803,62</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>R$ 161,42</t>
+          <t>-R$ 62.997,97</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1713626I</t>
+          <t>1713262</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5.318,80</t>
+          <t>2.675,61</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>R$ 5.318,80</t>
+          <t>R$ 2.675,61</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -4843,12 +4843,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1713656</t>
+          <t>1713351</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4.315,58</t>
+          <t>622,97</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>R$ 4.315,58</t>
+          <t>R$ 622,97</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -4875,12 +4875,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1713656I</t>
+          <t>1713435I</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>161,74</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 161,74</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4907,12 +4907,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1713660</t>
+          <t>1713626</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>161,11</t>
+          <t>161,42</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>R$ 161,11</t>
+          <t>R$ 161,42</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1713679</t>
+          <t>1713626I</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>3.574,44</t>
+          <t>5.318,80</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 3.574,44</t>
+          <t>R$ 5.318,80</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -4971,44 +4971,44 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1713681</t>
+          <t>1713656</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.473,94</t>
+          <t>4.315,58</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13.482,28</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-R$ 12.008,34</t>
+          <t>R$ 4.315,58</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>-89.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1713719</t>
+          <t>1713656I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3.385,92</t>
+          <t>161,74</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>R$ 3.385,92</t>
+          <t>R$ 161,74</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5035,12 +5035,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1713903C</t>
+          <t>1713660</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>36,14</t>
+          <t>161,11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>R$ 36,14</t>
+          <t>R$ 161,11</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5067,12 +5067,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1713903I</t>
+          <t>1713679</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>972,91</t>
+          <t>3.574,44</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>R$ 972,91</t>
+          <t>R$ 3.574,44</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5099,86 +5099,86 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1713933</t>
+          <t>1713681</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5.530,92</t>
+          <t>1.473,94</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.482,28</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>R$ 5.530,92</t>
+          <t>-R$ 12.008,34</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.1%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1714342</t>
+          <t>1713719</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2.011,96</t>
+          <t>3.385,92</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-R$ 20.176,01</t>
+          <t>R$ 3.385,92</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1714348</t>
+          <t>1713903C</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8.422,88</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>6.874,07</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>R$ 1.548,81</t>
+          <t>R$ 36,14</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5188,19 +5188,19 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>+22.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1714364</t>
+          <t>1713903I</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>54,64</t>
+          <t>972,91</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>R$ 54,64</t>
+          <t>R$ 972,91</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5227,86 +5227,86 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1714699</t>
+          <t>1713933</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>25.018,29</t>
+          <t>5.530,92</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>-R$ 30.004,58</t>
+          <t>R$ 5.530,92</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1714729</t>
+          <t>1714342</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6.722,61</t>
+          <t>2.011,96</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 6.722,61</t>
+          <t>-R$ 20.176,01</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-90.9%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1714857</t>
+          <t>1714348</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>185,07</t>
+          <t>8.422,88</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>6.874,07</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 185,07</t>
+          <t>R$ 1.548,81</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5316,19 +5316,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+22.5%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1714909</t>
+          <t>1714364</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1.062,57</t>
+          <t>54,64</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>R$ 1.062,57</t>
+          <t>R$ 54,64</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5355,44 +5355,44 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1715127</t>
+          <t>1714699</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>4.547,25</t>
+          <t>25.018,29</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 4.547,25</t>
+          <t>-R$ 30.004,58</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1715131</t>
+          <t>1714729</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2.220,22</t>
+          <t>6.722,61</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 2.220,22</t>
+          <t>R$ 6.722,61</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5419,12 +5419,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1715154</t>
+          <t>1714857</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2.658,74</t>
+          <t>185,07</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>R$ 2.658,74</t>
+          <t>R$ 185,07</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5451,12 +5451,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1715201</t>
+          <t>1714909</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>6.990,57</t>
+          <t>1.062,57</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>R$ 6.990,57</t>
+          <t>R$ 1.062,57</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5483,12 +5483,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1715257I</t>
+          <t>1715127</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6.765,65</t>
+          <t>4.547,25</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>R$ 6.765,65</t>
+          <t>R$ 4.547,25</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5515,12 +5515,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1715278</t>
+          <t>1715131</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2.961,13</t>
+          <t>2.220,22</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>R$ 2.961,13</t>
+          <t>R$ 2.220,22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5547,12 +5547,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1715327</t>
+          <t>1715154</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5.483,37</t>
+          <t>2.658,74</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>R$ 5.483,37</t>
+          <t>R$ 2.658,74</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5579,12 +5579,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1715668</t>
+          <t>1715201</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2.319,53</t>
+          <t>6.990,57</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>R$ 2.319,53</t>
+          <t>R$ 6.990,57</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5611,44 +5611,44 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1715688</t>
+          <t>1715257I</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>11.094,98</t>
+          <t>6.765,65</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>-R$ 62.706,61</t>
+          <t>R$ 6.765,65</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1715710</t>
+          <t>1715278</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>326,74</t>
+          <t>2.961,13</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 326,74</t>
+          <t>R$ 2.961,13</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1715816C</t>
+          <t>1715327</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>30,22</t>
+          <t>5.483,37</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>R$ 30,22</t>
+          <t>R$ 5.483,37</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -5707,12 +5707,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1715816I</t>
+          <t>1715668</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3.168,40</t>
+          <t>2.319,53</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>R$ 3.168,40</t>
+          <t>R$ 2.319,53</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -5739,76 +5739,76 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1715878</t>
+          <t>1715688</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.786,71</t>
+          <t>11.094,98</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>R$ 1.786,71</t>
+          <t>-R$ 62.706,61</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1715899</t>
+          <t>1715710</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3.389,65</t>
+          <t>326,74</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>-R$ 26.761,13</t>
+          <t>R$ 326,74</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1715920</t>
+          <t>1715816C</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1.031,94</t>
+          <t>30,22</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>R$ 1.031,94</t>
+          <t>R$ 30,22</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -5835,12 +5835,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1715955I</t>
+          <t>1715816I</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.970,68</t>
+          <t>3.168,40</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>R$ 2.970,68</t>
+          <t>R$ 3.168,40</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -5867,54 +5867,54 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1716557</t>
+          <t>1715878</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>81.673,94</t>
+          <t>1.786,71</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>219.995,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>-R$ 138.321,43</t>
+          <t>R$ 1.786,71</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1717166</t>
+          <t>1715899</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>22.116,83</t>
+          <t>3.389,65</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>-R$ 51.684,76</t>
+          <t>-R$ 26.761,13</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -5924,125 +5924,125 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1717168</t>
+          <t>1715920</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2.615,74</t>
+          <t>1.031,94</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>-R$ 27.535,04</t>
+          <t>R$ 1.031,94</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-91.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1717315</t>
+          <t>1715955I</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>13.183,29</t>
+          <t>4.431,48</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>13.214,86</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>-R$ 31,57</t>
+          <t>R$ 4.431,48</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1717332</t>
+          <t>1716557</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2.496,51</t>
+          <t>81.673,94</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>219.995,37</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>R$ 2.496,51</t>
+          <t>-R$ 138.321,43</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1718019</t>
+          <t>1717166</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>4.408,31</t>
+          <t>22.116,83</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>-R$ 24.366,14</t>
+          <t>-R$ 51.684,76</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6052,29 +6052,29 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1718435</t>
+          <t>1717168</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>17.153,90</t>
+          <t>2.615,74</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>-R$ 23.563,47</t>
+          <t>-R$ 27.535,04</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6084,51 +6084,51 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-91.3%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1718442</t>
+          <t>1717315</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>3.206,15</t>
+          <t>13.183,29</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>13.214,86</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>R$ 3.206,15</t>
+          <t>-R$ 31,57</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1718555I</t>
+          <t>1717332</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2.781,60</t>
+          <t>2.496,51</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>R$ 2.781,60</t>
+          <t>R$ 2.496,51</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6155,108 +6155,108 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1718561</t>
+          <t>1718019</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>15.227,27</t>
+          <t>4.408,31</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>R$ 15.227,27</t>
+          <t>-R$ 24.366,14</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1718783</t>
+          <t>1718435</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>16.983,02</t>
+          <t>17.153,90</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>R$ 16.983,02</t>
+          <t>-R$ 23.563,47</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-57.9%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1718783C</t>
+          <t>1718442</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>3.206,15</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>40.717,37</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>-R$ 40.710,05</t>
+          <t>R$ 3.206,15</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>-100.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1718803</t>
+          <t>1718555</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>3.825,18</t>
+          <t>80,49</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>R$ 3.825,18</t>
+          <t>R$ 80,49</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6283,118 +6283,118 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1718951</t>
+          <t>1718555I</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>257,86</t>
+          <t>2.781,60</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>-R$ 58.945,79</t>
+          <t>R$ 2.781,60</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-99.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1718954</t>
+          <t>1718561</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>16.304,49</t>
+          <t>15.227,27</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>-R$ 29.548,55</t>
+          <t>R$ 15.227,27</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>-64.4%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1718956</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>34.745,40</t>
+          <t>16.983,02</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>104.023,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>-R$ 69.278,38</t>
+          <t>R$ 16.983,02</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1718958</t>
+          <t>1718783C</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>28.287,18</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>45.853,04</t>
+          <t>40.717,37</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>-R$ 17.565,86</t>
+          <t>-R$ 40.710,05</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6404,19 +6404,19 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-100.0%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1719070</t>
+          <t>1718803</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>3.077,85</t>
+          <t>3.825,18</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>R$ 3.077,85</t>
+          <t>R$ 3.825,18</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -6443,22 +6443,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1719077</t>
+          <t>1718951</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>9.937,52</t>
+          <t>257,86</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>-R$ 45.453,71</t>
+          <t>-R$ 58.945,79</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -6468,29 +6468,29 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-99.6%</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1719097</t>
+          <t>1718954</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7.450,28</t>
+          <t>16.304,49</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>-R$ 10.084,35</t>
+          <t>-R$ 29.548,55</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -6500,61 +6500,61 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-64.4%</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1719135</t>
+          <t>1718956</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>960,92</t>
+          <t>34.745,40</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>104.023,78</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>R$ 960,92</t>
+          <t>-R$ 69.278,38</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-66.6%</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1719154</t>
+          <t>1718958</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2.574,70</t>
+          <t>28.287,18</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>73.801,59</t>
+          <t>45.853,04</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>-R$ 71.226,89</t>
+          <t>-R$ 17.565,86</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6564,61 +6564,61 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1719070</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2.368,97</t>
+          <t>3.077,85</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>-R$ 27.781,81</t>
+          <t>R$ 3.077,85</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>-92.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1719159</t>
+          <t>1719077</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2.240,81</t>
+          <t>12.241,72</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>-R$ 19.947,16</t>
+          <t>-R$ 43.149,51</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -6628,29 +6628,29 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>-89.9%</t>
+          <t>-77.9%</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1719213</t>
+          <t>1719097</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>7.323,19</t>
+          <t>7.450,28</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>-R$ 22.827,59</t>
+          <t>-R$ 10.084,35</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -6660,61 +6660,61 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1719214</t>
+          <t>1719135</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>6.124,60</t>
+          <t>960,92</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>-R$ 22.649,85</t>
+          <t>R$ 960,92</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1719775</t>
+          <t>1719154</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>6.946,00</t>
+          <t>2.574,70</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>73.801,59</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>-R$ 3.836,30</t>
+          <t>-R$ 71.226,89</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -6724,93 +6724,93 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1719881</t>
+          <t>1719155</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3.239,73</t>
+          <t>2.368,97</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>R$ 3.239,73</t>
+          <t>-R$ 27.781,81</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-92.1%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1719881H</t>
+          <t>1719159</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>38.258,42</t>
+          <t>2.240,81</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>R$ 38.258,42</t>
+          <t>-R$ 19.947,16</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-89.9%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1720116</t>
+          <t>1719213</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>1.844,52</t>
+          <t>7.323,19</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>28.774,45</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>-R$ 26.929,93</t>
+          <t>-R$ 22.827,59</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -6820,29 +6820,29 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1720721</t>
+          <t>1719214</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2.015,45</t>
+          <t>6.124,60</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>-R$ 15.519,18</t>
+          <t>-R$ 22.649,85</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -6852,29 +6852,29 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-78.7%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1720909</t>
+          <t>1719775</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2.851,89</t>
+          <t>6.946,00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>7.731,21</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>-R$ 4.879,32</t>
+          <t>-R$ 3.836,30</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -6884,51 +6884,51 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-35.6%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1720914</t>
+          <t>1719881</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>16.536,50</t>
+          <t>3.239,73</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>-R$ 38.486,37</t>
+          <t>R$ 3.239,73</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>-69.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1720920</t>
+          <t>1719881H</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>644,89</t>
+          <t>38.258,42</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>R$ 644,89</t>
+          <t>R$ 38.258,42</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -6955,22 +6955,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1721175</t>
+          <t>1720116</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1.191,73</t>
+          <t>1.844,52</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>28.774,45</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>-R$ 20.996,24</t>
+          <t>-R$ 26.929,93</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -6980,29 +6980,29 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-93.6%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1721595</t>
+          <t>1720721</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2.704,41</t>
+          <t>2.015,45</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>16.337,54</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>-R$ 13.633,13</t>
+          <t>-R$ 15.519,18</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7012,61 +7012,61 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-88.5%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1721631</t>
+          <t>1720909</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>12.649,43</t>
+          <t>2.851,89</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>R$ 12.649,43</t>
+          <t>-R$ 4.879,32</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-63.1%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1721631C</t>
+          <t>1720914</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>100,65</t>
+          <t>16.536,50</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>17.534,63</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>-R$ 17.433,98</t>
+          <t>-R$ 38.486,37</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -7076,61 +7076,61 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-69.9%</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1721869</t>
+          <t>1720920</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>940,27</t>
+          <t>644,89</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>-R$ 24.061,83</t>
+          <t>R$ 644,89</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>-96.2%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1721884</t>
+          <t>1721175</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>41.481,66</t>
+          <t>1.191,73</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>-R$ 163.783,49</t>
+          <t>-R$ 20.996,24</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7140,29 +7140,29 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1721886</t>
+          <t>1721595</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>14.551,70</t>
+          <t>2.704,41</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>55.022,87</t>
+          <t>16.337,54</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>-R$ 40.471,17</t>
+          <t>-R$ 13.633,13</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7172,61 +7172,61 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1721887</t>
+          <t>1721631</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>15.229,27</t>
+          <t>12.649,43</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>-R$ 45.688,83</t>
+          <t>R$ 12.649,43</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1722165</t>
+          <t>1721631C</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>23.880,34</t>
+          <t>100,65</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>294.803,26</t>
+          <t>17.534,63</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>-R$ 270.922,92</t>
+          <t>-R$ 17.433,98</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7236,61 +7236,61 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1722169</t>
+          <t>1721869</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>39.464,29</t>
+          <t>940,27</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>R$ 39.464,29</t>
+          <t>-R$ 24.061,83</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-96.2%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1722320</t>
+          <t>1721884</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>12.790,83</t>
+          <t>41.481,66</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>30.150,78</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>-R$ 17.359,95</t>
+          <t>-R$ 163.783,49</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -7300,29 +7300,29 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>-57.6%</t>
+          <t>-79.8%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1722321</t>
+          <t>1721886</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>8.119,58</t>
+          <t>14.551,70</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>55.022,87</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>-R$ 52.798,52</t>
+          <t>-R$ 40.471,17</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7332,29 +7332,29 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>-86.7%</t>
+          <t>-73.6%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1722779</t>
+          <t>1721887</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>15.490,41</t>
+          <t>15.229,27</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>205.265,15</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-R$ 189.774,74</t>
+          <t>-R$ 45.688,83</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -7364,29 +7364,29 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-75.0%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1722803</t>
+          <t>1722165</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>1.585,72</t>
+          <t>23.880,34</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>52.950,36</t>
+          <t>294.803,26</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>-R$ 51.364,64</t>
+          <t>-R$ 270.922,92</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -7396,61 +7396,61 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>-97.0%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1722904</t>
+          <t>1722169</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2.417,20</t>
+          <t>39.464,29</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>-R$ 22.584,90</t>
+          <t>R$ 39.464,29</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>-90.3%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1723691</t>
+          <t>1722320</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>19.599,32</t>
+          <t>12.790,83</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>30.150,78</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>-R$ 131.896,02</t>
+          <t>-R$ 17.359,95</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -7460,29 +7460,29 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-57.6%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1723722</t>
+          <t>1722321</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>3.175,84</t>
+          <t>8.119,58</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>10.782,30</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>-R$ 7.606,46</t>
+          <t>-R$ 52.798,52</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -7492,29 +7492,29 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-86.7%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1724051I</t>
+          <t>1722779</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2.432,48</t>
+          <t>15.490,41</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>205.265,15</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>-R$ 149.062,86</t>
+          <t>-R$ 189.774,74</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -7524,29 +7524,29 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1724053</t>
+          <t>1722803</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>3.088,86</t>
+          <t>1.585,72</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>151.495,34</t>
+          <t>52.950,36</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>-R$ 148.406,48</t>
+          <t>-R$ 51.364,64</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -7556,29 +7556,29 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>-98.0%</t>
+          <t>-97.0%</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1724172</t>
+          <t>1722904</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>23.068,97</t>
+          <t>2.417,20</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>-R$ 37.849,13</t>
+          <t>-R$ 22.584,90</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -7588,61 +7588,61 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-90.3%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1724341</t>
+          <t>1723691</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>40.758,00</t>
+          <t>19.599,32</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>R$ 40.758,00</t>
+          <t>-R$ 131.896,02</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-87.1%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1724356</t>
+          <t>1723694</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>7.614,80</t>
+          <t>3.867,23</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>60.918,10</t>
+          <t>7.731,21</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>-R$ 53.303,30</t>
+          <t>-R$ 3.863,98</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -7652,29 +7652,29 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-50.0%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1724491</t>
+          <t>1723722</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14.410,93</t>
+          <t>3.175,84</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>24.535,37</t>
+          <t>10.782,30</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>-R$ 10.124,44</t>
+          <t>-R$ 7.606,46</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -7684,29 +7684,29 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1724537</t>
+          <t>1724051I</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>6.077,43</t>
+          <t>2.432,48</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>-R$ 13.137,83</t>
+          <t>-R$ 149.062,86</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -7716,29 +7716,29 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1724550</t>
+          <t>1724053</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>17.067,84</t>
+          <t>3.088,86</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>55.391,23</t>
+          <t>151.495,34</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>-R$ 38.323,39</t>
+          <t>-R$ 148.406,48</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -7748,29 +7748,29 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-98.0%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1724551</t>
+          <t>1724172</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>8.569,24</t>
+          <t>23.068,97</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>-R$ 50.634,41</t>
+          <t>-R$ 37.849,13</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -7780,61 +7780,61 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-62.1%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1724663</t>
+          <t>1724341</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>3.091,28</t>
+          <t>40.758,00</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>22.187,97</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>-R$ 19.096,69</t>
+          <t>R$ 40.758,00</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>-86.1%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1725260</t>
+          <t>1724356</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>4.726,63</t>
+          <t>7.614,80</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>30.884,03</t>
+          <t>60.918,10</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>-R$ 26.157,40</t>
+          <t>-R$ 53.303,30</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -7844,19 +7844,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>-84.7%</t>
+          <t>-87.5%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1725686</t>
+          <t>1724491</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>11.172,87</t>
+          <t>14.410,93</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>-R$ 13.362,50</t>
+          <t>-R$ 10.124,44</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -7876,29 +7876,29 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>-54.5%</t>
+          <t>-41.3%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1725738C</t>
+          <t>1724537</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>146,69</t>
+          <t>8.464,00</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>-R$ 24.855,41</t>
+          <t>-R$ 10.751,26</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -7908,29 +7908,29 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>-99.4%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1725738I</t>
+          <t>1724550</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>16.959,62</t>
+          <t>17.067,84</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>25.002,10</t>
+          <t>55.391,23</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>-R$ 8.042,48</t>
+          <t>-R$ 38.323,39</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -7940,61 +7940,61 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1725869</t>
+          <t>1724551</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2.488,83</t>
+          <t>8.569,24</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>59.203,65</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>R$ 2.488,83</t>
+          <t>-R$ 50.634,41</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1726007</t>
+          <t>1724663</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>37.360,00</t>
+          <t>3.091,28</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>140.684,13</t>
+          <t>22.187,97</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>-R$ 103.324,13</t>
+          <t>-R$ 19.096,69</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -8004,29 +8004,29 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-86.1%</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1726008</t>
+          <t>1725260</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>96.656,83</t>
+          <t>4.726,63</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>203.193,73</t>
+          <t>30.884,03</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>-R$ 106.536,90</t>
+          <t>-R$ 26.157,40</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -8036,29 +8036,29 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1726018</t>
+          <t>1725686</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>43.320,32</t>
+          <t>11.172,87</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>189.306,13</t>
+          <t>24.535,37</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>-R$ 145.985,81</t>
+          <t>-R$ 13.362,50</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -8068,29 +8068,29 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-54.5%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1726042</t>
+          <t>1725738C</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>52.831,30</t>
+          <t>146,69</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>192.548,30</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>-R$ 139.717,00</t>
+          <t>-R$ 24.855,41</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -8100,29 +8100,29 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-99.4%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1726044</t>
+          <t>1725738I</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>163.324,35</t>
+          <t>16.959,62</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>167.292,84</t>
+          <t>25.002,10</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>-R$ 3.968,49</t>
+          <t>-R$ 8.042,48</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -8132,61 +8132,61 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1726045</t>
+          <t>1725869</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>114.693,62</t>
+          <t>2.488,83</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>126.996,75</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>-R$ 12.303,13</t>
+          <t>R$ 2.488,83</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1726057</t>
+          <t>1726007</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>177.769,55</t>
+          <t>92.044,51</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>196.508,79</t>
+          <t>140.684,13</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>-R$ 18.739,24</t>
+          <t>-R$ 48.639,62</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -8196,29 +8196,29 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-34.6%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1726058</t>
+          <t>1726008</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>103.529,88</t>
+          <t>96.656,83</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>133.354,34</t>
+          <t>203.193,73</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>-R$ 29.824,46</t>
+          <t>-R$ 106.536,90</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -8228,29 +8228,29 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-52.4%</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1726324</t>
+          <t>1726018</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2.294,20</t>
+          <t>117.487,61</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>189.306,13</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>-R$ 16.921,06</t>
+          <t>-R$ 71.818,52</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -8260,29 +8260,29 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>-88.1%</t>
+          <t>-37.9%</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1726332</t>
+          <t>1726042</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>5.722,23</t>
+          <t>52.831,30</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>192.548,30</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>-R$ 23.174,51</t>
+          <t>-R$ 139.717,00</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -8292,29 +8292,29 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-72.6%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1726496</t>
+          <t>1726044</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>24.645,05</t>
+          <t>163.324,35</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>167.292,84</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>-R$ 17.455,78</t>
+          <t>-R$ 3.968,49</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -8324,29 +8324,29 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1726890</t>
+          <t>1726045</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>3.252,02</t>
+          <t>114.693,62</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>11.143,51</t>
+          <t>126.996,75</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>-R$ 7.891,49</t>
+          <t>-R$ 12.303,13</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -8356,93 +8356,93 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1727187</t>
+          <t>1726057</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>4.280,60</t>
+          <t>177.769,55</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>196.508,79</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>R$ 4.280,60</t>
+          <t>-R$ 18.739,24</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.5%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1727287</t>
+          <t>1726058</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>489,21</t>
+          <t>103.529,88</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>133.354,34</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>R$ 489,21</t>
+          <t>-R$ 29.824,46</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-22.4%</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1727322</t>
+          <t>1726324</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3.146,66</t>
+          <t>2.294,20</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>-R$ 8.104,28</t>
+          <t>-R$ 16.921,06</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -8452,29 +8452,29 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-88.1%</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1727335</t>
+          <t>1726332</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>5.053,73</t>
+          <t>5.722,23</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>8.079,08</t>
+          <t>28.896,74</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>-R$ 3.025,35</t>
+          <t>-R$ 23.174,51</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>-37.4%</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1727529</t>
+          <t>1726496</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>4.366,81</t>
+          <t>24.645,05</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>42.100,83</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>-R$ 6.884,13</t>
+          <t>-R$ 17.455,78</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8516,51 +8516,51 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>-41.5%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1727778</t>
+          <t>1726890</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>3.846,49</t>
+          <t>3.252,02</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>11.143,51</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>R$ 3.846,49</t>
+          <t>-R$ 7.891,49</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-70.8%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1727808</t>
+          <t>1727187</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>4.280,60</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 4.280,60</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -8587,54 +8587,54 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1727808I</t>
+          <t>1727287</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2.562,33</t>
+          <t>489,21</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>8.676,98</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>-R$ 6.114,65</t>
+          <t>R$ 489,21</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1728055</t>
+          <t>1727322</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>12.947,91</t>
+          <t>3.146,66</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>42.100,83</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>-R$ 29.152,92</t>
+          <t>-R$ 8.104,28</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8644,61 +8644,61 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1728163</t>
+          <t>1727335</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>7.914,69</t>
+          <t>5.053,73</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>8.079,08</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>R$ 7.914,69</t>
+          <t>-R$ 3.025,35</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>✅ LUCRO</t>
+          <t>❌ PREJUÍZO</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-37.4%</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1728642</t>
+          <t>1727529</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7.237,16</t>
+          <t>4.366,81</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>19.215,26</t>
+          <t>11.250,94</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>-R$ 11.978,10</t>
+          <t>-R$ 6.884,13</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8708,93 +8708,93 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>-62.3%</t>
+          <t>-61.2%</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1729668</t>
+          <t>1727778</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>1.201,81</t>
+          <t>3.846,49</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>13.305,24</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>-R$ 12.103,43</t>
+          <t>R$ 3.846,49</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>-91.0%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1729828</t>
+          <t>1727808</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>914,81</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>11.250,94</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>-R$ 10.336,13</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1730222</t>
+          <t>1727808I</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>21.764,18</t>
+          <t>2.562,33</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>28.896,74</t>
+          <t>8.676,98</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>-R$ 7.132,56</t>
+          <t>-R$ 6.114,65</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8804,19 +8804,19 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-70.5%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1730270</t>
+          <t>1728055</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>10.340,91</t>
+          <t>12.947,91</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>-R$ 31.759,92</t>
+          <t>-R$ 29.152,92</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8836,61 +8836,61 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1730763</t>
+          <t>1728163</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>4.973,33</t>
+          <t>7.914,69</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>59.203,65</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>-R$ 54.230,32</t>
+          <t>R$ 7.914,69</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>❌ PREJUÍZO</t>
+          <t>✅ LUCRO</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>-91.6%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1730822</t>
+          <t>1728642</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>30.861,26</t>
+          <t>7.237,16</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>68.930,71</t>
+          <t>19.215,26</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>-R$ 38.069,45</t>
+          <t>-R$ 11.978,10</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -8900,29 +8900,29 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>-55.2%</t>
+          <t>-62.3%</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1730908</t>
+          <t>1729668</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>4.386,39</t>
+          <t>1.201,81</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>17.270,31</t>
+          <t>13.305,24</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>-R$ 12.883,92</t>
+          <t>-R$ 12.103,43</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -8932,39 +8932,327 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-91.0%</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>1729786</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>45.387,32</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>44.264,28</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>R$ 1.123,04</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>+2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1729828</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>914,81</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>11.250,94</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>-R$ 10.336,13</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-91.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1730222</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>21.764,18</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>28.896,74</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>-R$ 7.132,56</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-24.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1730270</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>10.340,91</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>42.100,83</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>-R$ 31.759,92</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-75.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1730642I</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>15.899,82</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>20.657,21</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>-R$ 4.757,39</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-23.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1730763</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>4.973,33</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>59.203,65</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>-R$ 54.230,32</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-91.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1730822</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>31.373,82</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>68.930,71</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>-R$ 37.556,89</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-54.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1730908</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>4.386,39</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>17.270,31</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-R$ 12.883,92</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-74.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
           <t>1731653</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>5.940,43</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
         <is>
           <t>R$ 5.940,43</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>✅ LUCRO</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>✅ LUCRO</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1734449</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>10.662,83</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>46.847,53</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>-R$ 36.184,70</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>❌ PREJUÍZO</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-77.2%</t>
         </is>
       </c>
     </row>
